--- a/results/job_matches_2026-04-14.xlsx
+++ b/results/job_matches_2026-04-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>SentiLink</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d78327146c19a784</t>
+          <t>https://www.indeed.com/viewjob?jk=e1963992b9015fbc</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Full Stack Engineer - AI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f47248faf88df34</t>
+          <t>https://www.indeed.com/viewjob?jk=f2cc2730bd14a3e8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2cc2730bd14a3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=8cba17f74f3a8a87</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>metropolis</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cba17f74f3a8a87</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc5289c2eff0fe3</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>metropolis</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc5289c2eff0fe3</t>
+          <t>https://www.indeed.com/viewjob?jk=0db447e4c4e1f04b</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db447e4c4e1f04b</t>
+          <t>https://www.indeed.com/viewjob?jk=b55ea3b297953077</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55ea3b297953077</t>
+          <t>https://www.indeed.com/viewjob?jk=d857667edacbcc1e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>EMR, Redshift, S3, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d857667edacbcc1e</t>
+          <t>https://www.indeed.com/viewjob?jk=7529728374eb4213</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Machine Learning</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EMR, Redshift, S3, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7529728374eb4213</t>
+          <t>https://www.indeed.com/viewjob?jk=a513718316ea30dd</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ML Infrastructure/Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6121915b4e45790d</t>
+          <t>https://www.indeed.com/viewjob?jk=43cfe33e6a3659da</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,24 +1151,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25e97510ea5ed940</t>
+          <t>https://www.indeed.com/viewjob?jk=620e166ed5473039</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ML Infrastructure/Platform Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1178,15 +1178,15 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,102 +1196,102 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72b0fdeb9512d34e</t>
+          <t>https://www.indeed.com/viewjob?jk=6121915b4e45790d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b78c747cdda3eb</t>
+          <t>https://www.indeed.com/viewjob?jk=25e97510ea5ed940</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Credential API</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c29ef248c94981</t>
+          <t>https://www.indeed.com/viewjob?jk=79c136294cfd98fe</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer - United States</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>William Blair &amp; Company</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cea3dbea7cb13bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=04db638500700cb1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Applications Developer</t>
+          <t>Software Engineer 3 - Contingent (contract)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,19 +1336,19 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5622a97c0cb32459</t>
+          <t>https://www.indeed.com/viewjob?jk=7051fd3bf67a37ac</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AWS Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Synergy BIS</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1357,11 +1357,11 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, PostgreSQL, MySQL, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbf74cf2b06a65f1</t>
+          <t>https://www.indeed.com/viewjob?jk=72b0fdeb9512d34e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sys. Integration Sr. Specialist Advisor</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e632ec94c82b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b78c747cdda3eb</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sys. Integration Sr. Specialist Advisor</t>
+          <t>Software Development Engineer - Credential API</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,102 +1441,102 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aca172869e592e8</t>
+          <t>https://www.indeed.com/viewjob?jk=88c29ef248c94981</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>William Blair &amp; Company</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2444333527505cd</t>
+          <t>https://www.indeed.com/viewjob?jk=cea3dbea7cb13bbf</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Applications Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee60578e0abfdb96</t>
+          <t>https://www.indeed.com/viewjob?jk=5622a97c0cb32459</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer/Sr Data Engineer</t>
+          <t>Data Reliability Engineer Oncology Analytics</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Georgia-Pacific</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Step Functions, S3, IAM, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,102 +1546,102 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f129032e6f84d172</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a8530ac9c848be</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Synergy BIS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, PostgreSQL, MySQL, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed57d3552234a972</t>
+          <t>https://www.indeed.com/viewjob?jk=dbf74cf2b06a65f1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Sys. Integration Sr. Specialist Advisor</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f675cb5511b3a92e</t>
+          <t>https://www.indeed.com/viewjob?jk=43e632ec94c82b3b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IT Data Developer</t>
+          <t>Sys. Integration Sr. Specialist Advisor</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tempur + Sealy</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Trinity, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Spark, PySpark, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,137 +1651,137 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d7106826dcc9d2</t>
+          <t>https://www.indeed.com/viewjob?jk=1aca172869e592e8</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f1c7ebf3cba3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=c2444333527505cd</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b40f262a4271a7</t>
+          <t>https://www.indeed.com/viewjob?jk=ee60578e0abfdb96</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Intermediate Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, Azure, Hadoop, Spark, Dask, Snowflake, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e4bcd62747c894</t>
+          <t>https://www.indeed.com/viewjob?jk=2ccec05543d43588</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>Data Engineer/Sr Data Engineer (NOT OPEN TO VISA HOLDERS)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JobSPOT</t>
+          <t>Georgia-Pacific</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, Redshift, Step Functions, S3, IAM, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d30905e392635ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=f129032e6f84d172</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr Web Software Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mouser Electronics</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mansfield, TX, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=336c0c1bf86693ef</t>
+          <t>https://www.indeed.com/viewjob?jk=ed57d3552234a972</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Hifi</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7522730840daa67d</t>
+          <t>https://www.indeed.com/viewjob?jk=6177a38e86fbab44</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d727c9d934f72b</t>
+          <t>https://www.indeed.com/viewjob?jk=2722db66dd139366</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Path Robotics, Inc.</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0c06f03d80ad17</t>
+          <t>https://www.indeed.com/viewjob?jk=a1567499d777de5d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3fa7b3be8f9a0fb</t>
+          <t>https://www.indeed.com/viewjob?jk=f675cb5511b3a92e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>IT Data Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Tempur + Sealy</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Trinity, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Spark, PySpark, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3e97aaf28d0108</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d7106826dcc9d2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410def4f54721f1a</t>
+          <t>https://www.indeed.com/viewjob?jk=02ca8eea8c20d4f1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8c2e004e287ec36</t>
+          <t>https://www.indeed.com/viewjob?jk=fd62970232a35032</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55d3d996d9d61dc</t>
+          <t>https://www.indeed.com/viewjob?jk=e94dc1bfd30ae5f1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf1e7e97badd9a1</t>
+          <t>https://www.indeed.com/viewjob?jk=ffb45764baeec647</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Operations Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0786555ef46de3</t>
+          <t>https://www.indeed.com/viewjob?jk=93a9ff833b41ef5d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, (Production Excellence)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>Pluto TV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, MongoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f706322313ef04c9</t>
+          <t>https://www.indeed.com/viewjob?jk=46f1c7ebf3cba3e3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Trust &amp; Safety</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb78589d2a39e4df</t>
+          <t>https://www.indeed.com/viewjob?jk=10b40f262a4271a7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Rev Agency</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, Azure Cosmos DB, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,67 +2281,67 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eeab1f3de2ae00d</t>
+          <t>https://www.indeed.com/viewjob?jk=d78327146c19a784</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21cb7010e5a8a63</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e4bcd62747c894</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6d4850de30c8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=f8bde7b210d67def</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc22d977c810f0a5</t>
+          <t>https://www.indeed.com/viewjob?jk=dd96031899aef8e4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Entry-level Moment Google Contact Center Developer</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>JobSPOT</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26650088972ec91e</t>
+          <t>https://www.indeed.com/viewjob?jk=d30905e392635ceb</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Web Software Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AIA Contract Documents</t>
+          <t>Mouser Electronics</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mansfield, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,42 +2456,742 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27b382a0dd9b7c72</t>
+          <t>https://www.indeed.com/viewjob?jk=336c0c1bf86693ef</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>Software Engineer, Backend</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Hifi</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7522730840daa67d</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Precisely</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27d727c9d934f72b</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Path Robotics, Inc.</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a0c06f03d80ad17</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>RNGD</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Metairie, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f60859d558e50585</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Data &amp; Integrations Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Alternate Solutions Health Network</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3fa7b3be8f9a0fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Data and BI Solutions Developer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>ExtraMile</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a3e97aaf28d0108</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Data and BI Solutions Developer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ExtraMile</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=410def4f54721f1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Data and BI Solutions Developer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ExtraMile</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>AR, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8c2e004e287ec36</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Data and BI Solutions Developer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ExtraMile</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b55d3d996d9d61dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Data and BI Solutions Developer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ExtraMile</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=faf1e7e97badd9a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Data Engineering &amp; Operations Specialist</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Shelter Insurance</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Columbia, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac0786555ef46de3</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer, (Production Excellence)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Poshmark</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Redwood City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, MongoDB, CI/CD, Jenkins, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f706322313ef04c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Full stack)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>People People</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, PostgreSQL, CI/CD, CodeBuild</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7430c49b9feec362</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Match Group</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kubernetes, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb78589d2a39e4df</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java [Hybrid]</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f21cb7010e5a8a63</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java [Hybrid]</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a6d4850de30c8ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java [Hybrid]</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc22d977c810f0a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>AIA Contract Documents</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27b382a0dd9b7c72</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Entry-level Moment Google Contact Center Developer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26650088972ec91e</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
           <t>Solution Engineer - Data Engineering Specialist - Bilingual (Spanish)</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>Snowflake</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>GA, US USA</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D78" t="n">
         <v>10.4</v>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=92a26823ec6dae45</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Senior Python Developer (Cloud – GCP/Azure) (Remote)</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Bentonville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, PySpark, Scala, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4f629c97031e8ed</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-14.xlsx
+++ b/results/job_matches_2026-04-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Parker's Kitchen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Sqoop, HBase, Flume, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8855ef540e8dc9e8</t>
+          <t>https://www.indeed.com/viewjob?jk=403fe46aec3ac312</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Parker's Kitchen</t>
+          <t>Parker Management</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403fe46aec3ac312</t>
+          <t>https://www.indeed.com/viewjob?jk=43381ea07fee685f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Parker Management</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Sqoop, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43381ea07fee685f</t>
+          <t>https://www.indeed.com/viewjob?jk=8855ef540e8dc9e8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Engineer, Software</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SwapsTech</t>
+          <t>Verint Systems Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Oracle, MySQL</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4012ccd366ad2714</t>
+          <t>https://www.indeed.com/viewjob?jk=0c774765a5f06879</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Engineer, Software</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Verint Systems Inc.</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c774765a5f06879</t>
+          <t>https://www.indeed.com/viewjob?jk=83db8f50bcabcd87</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Full Stack Engineer - AI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83db8f50bcabcd87</t>
+          <t>https://www.indeed.com/viewjob?jk=f2cc2730bd14a3e8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2cc2730bd14a3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=a513718316ea30dd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cba17f74f3a8a87</t>
+          <t>https://www.indeed.com/viewjob?jk=43cfe33e6a3659da</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>metropolis</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,29 +906,29 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc5289c2eff0fe3</t>
+          <t>https://www.indeed.com/viewjob?jk=620e166ed5473039</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ML Infrastructure/Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db447e4c4e1f04b</t>
+          <t>https://www.indeed.com/viewjob?jk=6121915b4e45790d</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55ea3b297953077</t>
+          <t>https://www.indeed.com/viewjob?jk=8cba17f74f3a8a87</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>metropolis</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d857667edacbcc1e</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc5289c2eff0fe3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Machine Learning</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>EMR, Redshift, S3, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7529728374eb4213</t>
+          <t>https://www.indeed.com/viewjob?jk=0db447e4c4e1f04b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a513718316ea30dd</t>
+          <t>https://www.indeed.com/viewjob?jk=b55ea3b297953077</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43cfe33e6a3659da</t>
+          <t>https://www.indeed.com/viewjob?jk=d857667edacbcc1e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620e166ed5473039</t>
+          <t>https://www.indeed.com/viewjob?jk=25e97510ea5ed940</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ML Infrastructure/Platform Engineer</t>
+          <t>Sr. Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
+          <t>EMR, Redshift, S3, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6121915b4e45790d</t>
+          <t>https://www.indeed.com/viewjob?jk=7529728374eb4213</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,69 +1221,69 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25e97510ea5ed940</t>
+          <t>https://www.indeed.com/viewjob?jk=79c136294cfd98fe</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Data Engineer - United States</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79c136294cfd98fe</t>
+          <t>https://www.indeed.com/viewjob?jk=04db638500700cb1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer - United States</t>
+          <t>Software Engineer 3 - Contingent (contract)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04db638500700cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=7051fd3bf67a37ac</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer 3 - Contingent (contract)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7051fd3bf67a37ac</t>
+          <t>https://www.indeed.com/viewjob?jk=72b0fdeb9512d34e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72b0fdeb9512d34e</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b78c747cdda3eb</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Software Development Engineer - Credential API</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b78c747cdda3eb</t>
+          <t>https://www.indeed.com/viewjob?jk=88c29ef248c94981</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Credential API</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>William Blair &amp; Company</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c29ef248c94981</t>
+          <t>https://www.indeed.com/viewjob?jk=cea3dbea7cb13bbf</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Applications Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>William Blair &amp; Company</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cea3dbea7cb13bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=5622a97c0cb32459</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Applications Developer</t>
+          <t>Data Reliability Engineer Oncology Analytics</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5622a97c0cb32459</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a8530ac9c848be</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer Oncology Analytics</t>
+          <t>AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Synergy BIS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, ECS, RDS, PostgreSQL, MySQL, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a8530ac9c848be</t>
+          <t>https://www.indeed.com/viewjob?jk=dbf74cf2b06a65f1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AWS Platform Engineer</t>
+          <t>Sys. Integration Sr. Specialist Advisor</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Synergy BIS</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, PostgreSQL, MySQL, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbf74cf2b06a65f1</t>
+          <t>https://www.indeed.com/viewjob?jk=43e632ec94c82b3b</t>
         </is>
       </c>
     </row>
@@ -1616,14 +1616,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e632ec94c82b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=1aca172869e592e8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sys. Integration Sr. Specialist Advisor</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,104 +1641,104 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aca172869e592e8</t>
+          <t>https://www.indeed.com/viewjob?jk=c2444333527505cd</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Intermediate Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, Azure, Hadoop, Spark, Dask, Snowflake, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2444333527505cd</t>
+          <t>https://www.indeed.com/viewjob?jk=2ccec05543d43588</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer/Sr Data Engineer (NOT OPEN TO VISA HOLDERS)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Georgia-Pacific</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Redshift, Step Functions, S3, IAM, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee60578e0abfdb96</t>
+          <t>https://www.indeed.com/viewjob?jk=f129032e6f84d172</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Intermediate Machine Learning Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Spark, Dask, Snowflake, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ccec05543d43588</t>
+          <t>https://www.indeed.com/viewjob?jk=ed57d3552234a972</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer/Sr Data Engineer (NOT OPEN TO VISA HOLDERS)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Georgia-Pacific</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Step Functions, S3, IAM, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f129032e6f84d172</t>
+          <t>https://www.indeed.com/viewjob?jk=6177a38e86fbab44</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed57d3552234a972</t>
+          <t>https://www.indeed.com/viewjob?jk=2722db66dd139366</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6177a38e86fbab44</t>
+          <t>https://www.indeed.com/viewjob?jk=a1567499d777de5d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2722db66dd139366</t>
+          <t>https://www.indeed.com/viewjob?jk=f675cb5511b3a92e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>IT Data Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Tempur + Sealy</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Trinity, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Data Factory, Spark, PySpark, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1567499d777de5d</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d7106826dcc9d2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f675cb5511b3a92e</t>
+          <t>https://www.indeed.com/viewjob?jk=ffb45764baeec647</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>IT Data Developer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tempur + Sealy</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Trinity, NC, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Spark, PySpark, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d7106826dcc9d2</t>
+          <t>https://www.indeed.com/viewjob?jk=02ca8eea8c20d4f1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ca8eea8c20d4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=93a9ff833b41ef5d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Pluto TV</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd62970232a35032</t>
+          <t>https://www.indeed.com/viewjob?jk=46f1c7ebf3cba3e3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e94dc1bfd30ae5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=10b40f262a4271a7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, Azure Cosmos DB, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffb45764baeec647</t>
+          <t>https://www.indeed.com/viewjob?jk=d78327146c19a784</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93a9ff833b41ef5d</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e4bcd62747c894</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f1c7ebf3cba3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=fd62970232a35032</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b40f262a4271a7</t>
+          <t>https://www.indeed.com/viewjob?jk=e94dc1bfd30ae5f1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, Azure Cosmos DB, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d78327146c19a784</t>
+          <t>https://www.indeed.com/viewjob?jk=f8bde7b210d67def</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e4bcd62747c894</t>
+          <t>https://www.indeed.com/viewjob?jk=dd96031899aef8e4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>JobSPOT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8bde7b210d67def</t>
+          <t>https://www.indeed.com/viewjob?jk=d30905e392635ceb</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
+          <t>Sr Web Software Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Mouser Electronics</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mansfield, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,19 +2386,19 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd96031899aef8e4</t>
+          <t>https://www.indeed.com/viewjob?jk=336c0c1bf86693ef</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JobSPOT</t>
+          <t>Hifi</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d30905e392635ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=7522730840daa67d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Web Software Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mouser Electronics</t>
+          <t>Precisely</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Mansfield, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
+          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=336c0c1bf86693ef</t>
+          <t>https://www.indeed.com/viewjob?jk=27d727c9d934f72b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Hifi</t>
+          <t>RNGD</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7522730840daa67d</t>
+          <t>https://www.indeed.com/viewjob?jk=f60859d558e50585</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d727c9d934f72b</t>
+          <t>https://www.indeed.com/viewjob?jk=c3fa7b3be8f9a0fb</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Path Robotics, Inc.</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0c06f03d80ad17</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3e97aaf28d0108</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RNGD</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f60859d558e50585</t>
+          <t>https://www.indeed.com/viewjob?jk=410def4f54721f1a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3fa7b3be8f9a0fb</t>
+          <t>https://www.indeed.com/viewjob?jk=e8c2e004e287ec36</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3e97aaf28d0108</t>
+          <t>https://www.indeed.com/viewjob?jk=b55d3d996d9d61dc</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410def4f54721f1a</t>
+          <t>https://www.indeed.com/viewjob?jk=faf1e7e97badd9a1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Data Engineering &amp; Operations Specialist</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8c2e004e287ec36</t>
+          <t>https://www.indeed.com/viewjob?jk=ac0786555ef46de3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Senior Site Reliability Engineer, (Production Excellence)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, MongoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55d3d996d9d61dc</t>
+          <t>https://www.indeed.com/viewjob?jk=f706322313ef04c9</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Data Tester (Python) - 6254091</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, PySpark, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf1e7e97badd9a1</t>
+          <t>https://www.indeed.com/viewjob?jk=89141221ea154795</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Operations Specialist</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>Path Robotics, Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0786555ef46de3</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0c06f03d80ad17</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, (Production Excellence)</t>
+          <t>Senior Software Engineer (Full stack)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>People People</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, MongoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, PostgreSQL, CI/CD, CodeBuild</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f706322313ef04c9</t>
+          <t>https://www.indeed.com/viewjob?jk=7430c49b9feec362</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full stack)</t>
+          <t>Senior Machine Learning Engineer, Trust &amp; Safety</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>People People</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, PostgreSQL, CI/CD, CodeBuild</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7430c49b9feec362</t>
+          <t>https://www.indeed.com/viewjob?jk=fb78589d2a39e4df</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Trust &amp; Safety</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb78589d2a39e4df</t>
+          <t>https://www.indeed.com/viewjob?jk=f21cb7010e5a8a63</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21cb7010e5a8a63</t>
+          <t>https://www.indeed.com/viewjob?jk=5a6d4850de30c8ce</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6d4850de30c8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=dc22d977c810f0a5</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Entry-level Moment Google Contact Center Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc22d977c810f0a5</t>
+          <t>https://www.indeed.com/viewjob?jk=26650088972ec91e</t>
         </is>
       </c>
     </row>
@@ -3093,17 +3093,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Entry-level Moment Google Contact Center Developer</t>
+          <t>Solution Engineer - Data Engineering Specialist - Bilingual (Spanish)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26650088972ec91e</t>
+          <t>https://www.indeed.com/viewjob?jk=92a26823ec6dae45</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Solution Engineer - Data Engineering Specialist - Bilingual (Spanish)</t>
+          <t>Senior Python Developer (Cloud – GCP/Azure) (Remote)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,50 +3146,15 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, PySpark, Scala, Airflow, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=92a26823ec6dae45</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Senior Python Developer (Cloud – GCP/Azure) (Remote)</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Bentonville, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, PySpark, Scala, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c4f629c97031e8ed</t>
         </is>

--- a/results/job_matches_2026-04-14.xlsx
+++ b/results/job_matches_2026-04-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Parker's Kitchen</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Sqoop, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403fe46aec3ac312</t>
+          <t>https://www.indeed.com/viewjob?jk=8855ef540e8dc9e8</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Parker Management</t>
+          <t>Parker's Kitchen</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43381ea07fee685f</t>
+          <t>https://www.indeed.com/viewjob?jk=403fe46aec3ac312</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Parker Management</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Sqoop, HBase, Flume, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8855ef540e8dc9e8</t>
+          <t>https://www.indeed.com/viewjob?jk=43381ea07fee685f</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, EMR, Kinesis, Redshift, S3, Hadoop, Hive, MapReduce, HBase, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83db8f50bcabcd87</t>
+          <t>https://www.indeed.com/viewjob?jk=454945ebbe7d1ebf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data Engineering</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, S3, Hadoop, Hive, MapReduce, HBase, Spark</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454945ebbe7d1ebf</t>
+          <t>https://www.indeed.com/viewjob?jk=83db8f50bcabcd87</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - AI</t>
+          <t>Salesforce Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t xml:space="preserve">KPRMT Global solutions </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2cc2730bd14a3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=573c4c858dde7f71</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Engineer - AI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a513718316ea30dd</t>
+          <t>https://www.indeed.com/viewjob?jk=f2cc2730bd14a3e8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43cfe33e6a3659da</t>
+          <t>https://www.indeed.com/viewjob?jk=8cba17f74f3a8a87</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>metropolis</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,29 +906,29 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620e166ed5473039</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc5289c2eff0fe3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ML Infrastructure/Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6121915b4e45790d</t>
+          <t>https://www.indeed.com/viewjob?jk=0db447e4c4e1f04b</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cba17f74f3a8a87</t>
+          <t>https://www.indeed.com/viewjob?jk=b55ea3b297953077</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>metropolis</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc5289c2eff0fe3</t>
+          <t>https://www.indeed.com/viewjob?jk=d857667edacbcc1e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>EMR, Redshift, S3, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db447e4c4e1f04b</t>
+          <t>https://www.indeed.com/viewjob?jk=7529728374eb4213</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55ea3b297953077</t>
+          <t>https://www.indeed.com/viewjob?jk=a513718316ea30dd</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d857667edacbcc1e</t>
+          <t>https://www.indeed.com/viewjob?jk=43cfe33e6a3659da</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25e97510ea5ed940</t>
+          <t>https://www.indeed.com/viewjob?jk=620e166ed5473039</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Machine Learning</t>
+          <t>ML Infrastructure/Platform Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>EMR, Redshift, S3, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7529728374eb4213</t>
+          <t>https://www.indeed.com/viewjob?jk=6121915b4e45790d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,77 +1221,77 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79c136294cfd98fe</t>
+          <t>https://www.indeed.com/viewjob?jk=25e97510ea5ed940</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer - United States</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04db638500700cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=79c136294cfd98fe</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer 3 - Contingent (contract)</t>
+          <t>AWS Data Architect (Hybrid)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Signet Jewelers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Coppell, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, SQS, SNS, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,19 +1301,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7051fd3bf67a37ac</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0e64cf5300616c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - United States</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72b0fdeb9512d34e</t>
+          <t>https://www.indeed.com/viewjob?jk=04db638500700cb1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Software Engineer 3 - Contingent (contract)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b78c747cdda3eb</t>
+          <t>https://www.indeed.com/viewjob?jk=7051fd3bf67a37ac</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Credential API</t>
+          <t>Computing Architect (Mid-Level or Senior)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c29ef248c94981</t>
+          <t>https://www.indeed.com/viewjob?jk=8bda91a521ece52f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Enterprise Architect, Azure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>William Blair &amp; Company</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cea3dbea7cb13bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=890935458d36553e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Applications Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5622a97c0cb32459</t>
+          <t>https://www.indeed.com/viewjob?jk=72b0fdeb9512d34e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer Oncology Analytics</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a8530ac9c848be</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b78c747cdda3eb</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AWS Platform Engineer</t>
+          <t>Data Architect - C2H - Onsite</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Synergy BIS</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, PostgreSQL, MySQL, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbf74cf2b06a65f1</t>
+          <t>https://www.indeed.com/viewjob?jk=087dc81db4c0ead7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sys. Integration Sr. Specialist Advisor</t>
+          <t>Senior Applications Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e632ec94c82b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=5622a97c0cb32459</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sys. Integration Sr. Specialist Advisor</t>
+          <t>Software Development Engineer - Credential API</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,102 +1616,102 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aca172869e592e8</t>
+          <t>https://www.indeed.com/viewjob?jk=88c29ef248c94981</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>William Blair &amp; Company</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2444333527505cd</t>
+          <t>https://www.indeed.com/viewjob?jk=cea3dbea7cb13bbf</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Intermediate Machine Learning Data Engineer</t>
+          <t>Engineer II – Big Data / ETL Engineer (Apptio)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Spark, Dask, Snowflake, CI/CD, Jenkins, Azure DevOps</t>
+          <t>Databricks, BigQuery, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ccec05543d43588</t>
+          <t>https://www.indeed.com/viewjob?jk=be9de9e1e7dbc172</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer/Sr Data Engineer (NOT OPEN TO VISA HOLDERS)</t>
+          <t>Data Reliability Engineer Oncology Analytics</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Georgia-Pacific</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Step Functions, S3, IAM, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f129032e6f84d172</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a8530ac9c848be</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Synergy BIS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, PostgreSQL, MySQL, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed57d3552234a972</t>
+          <t>https://www.indeed.com/viewjob?jk=dbf74cf2b06a65f1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sys. Integration Sr. Specialist Advisor</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6177a38e86fbab44</t>
+          <t>https://www.indeed.com/viewjob?jk=43e632ec94c82b3b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Sys. Integration Sr. Specialist Advisor</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,59 +1826,59 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2722db66dd139366</t>
+          <t>https://www.indeed.com/viewjob?jk=1aca172869e592e8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1567499d777de5d</t>
+          <t>https://www.indeed.com/viewjob?jk=c2444333527505cd</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Intermediate Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, S3, Azure, Hadoop, Spark, Dask, Snowflake, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f675cb5511b3a92e</t>
+          <t>https://www.indeed.com/viewjob?jk=2ccec05543d43588</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>IT Data Developer</t>
+          <t>Data Engineer/Sr Data Engineer (NOT OPEN TO VISA HOLDERS)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tempur + Sealy</t>
+          <t>Georgia-Pacific</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Trinity, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Spark, PySpark, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Redshift, Step Functions, S3, IAM, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d7106826dcc9d2</t>
+          <t>https://www.indeed.com/viewjob?jk=f129032e6f84d172</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffb45764baeec647</t>
+          <t>https://www.indeed.com/viewjob?jk=ed57d3552234a972</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ca8eea8c20d4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=6177a38e86fbab44</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93a9ff833b41ef5d</t>
+          <t>https://www.indeed.com/viewjob?jk=2722db66dd139366</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f1c7ebf3cba3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=a1567499d777de5d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>IT Data Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Tempur + Sealy</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Trinity, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, Azure, Data Factory, Spark, PySpark, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,59 +2106,59 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b40f262a4271a7</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d7106826dcc9d2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, Azure Cosmos DB, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d78327146c19a784</t>
+          <t>https://www.indeed.com/viewjob?jk=f675cb5511b3a92e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e4bcd62747c894</t>
+          <t>https://www.indeed.com/viewjob?jk=02ca8eea8c20d4f1</t>
         </is>
       </c>
     </row>
@@ -2253,17 +2253,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
+          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8bde7b210d67def</t>
+          <t>https://www.indeed.com/viewjob?jk=ffb45764baeec647</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd96031899aef8e4</t>
+          <t>https://www.indeed.com/viewjob?jk=93a9ff833b41ef5d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JobSPOT</t>
+          <t>Pluto TV</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d30905e392635ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=46f1c7ebf3cba3e3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr Web Software Developer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mouser Electronics</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mansfield, TX, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=336c0c1bf86693ef</t>
+          <t>https://www.indeed.com/viewjob?jk=10b40f262a4271a7</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Hifi</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, Azure Cosmos DB, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7522730840daa67d</t>
+          <t>https://www.indeed.com/viewjob?jk=d78327146c19a784</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,42 +2446,42 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d727c9d934f72b</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e4bcd62747c894</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Web Software Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>RNGD</t>
+          <t>Mouser Electronics</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Mansfield, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f60859d558e50585</t>
+          <t>https://www.indeed.com/viewjob?jk=336c0c1bf86693ef</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3fa7b3be8f9a0fb</t>
+          <t>https://www.indeed.com/viewjob?jk=ac2463a9d29a6913</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3e97aaf28d0108</t>
+          <t>https://www.indeed.com/viewjob?jk=f8bde7b210d67def</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410def4f54721f1a</t>
+          <t>https://www.indeed.com/viewjob?jk=dd96031899aef8e4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>JobSPOT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8c2e004e287ec36</t>
+          <t>https://www.indeed.com/viewjob?jk=d30905e392635ceb</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Hifi</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55d3d996d9d61dc</t>
+          <t>https://www.indeed.com/viewjob?jk=7522730840daa67d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Precisely</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf1e7e97badd9a1</t>
+          <t>https://www.indeed.com/viewjob?jk=27d727c9d934f72b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Operations Specialist</t>
+          <t>Data Tester (Python) - 6254091</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, PySpark, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0786555ef46de3</t>
+          <t>https://www.indeed.com/viewjob?jk=89141221ea154795</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, (Production Excellence)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>Path Robotics, Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, MongoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f706322313ef04c9</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0c06f03d80ad17</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Tester (Python) - 6254091</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>RNGD</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, PySpark, ETL, ELT, CI/CD</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,19 +2806,19 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89141221ea154795</t>
+          <t>https://www.indeed.com/viewjob?jk=f60859d558e50585</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Path Robotics, Inc.</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0c06f03d80ad17</t>
+          <t>https://www.indeed.com/viewjob?jk=c3fa7b3be8f9a0fb</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full stack)</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>People People</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, PostgreSQL, CI/CD, CodeBuild</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7430c49b9feec362</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3e97aaf28d0108</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Trust &amp; Safety</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb78589d2a39e4df</t>
+          <t>https://www.indeed.com/viewjob?jk=410def4f54721f1a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21cb7010e5a8a63</t>
+          <t>https://www.indeed.com/viewjob?jk=e8c2e004e287ec36</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6d4850de30c8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=b55d3d996d9d61dc</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc22d977c810f0a5</t>
+          <t>https://www.indeed.com/viewjob?jk=faf1e7e97badd9a1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Entry-level Moment Google Contact Center Developer</t>
+          <t>Data Engineering &amp; Operations Specialist</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26650088972ec91e</t>
+          <t>https://www.indeed.com/viewjob?jk=ac0786555ef46de3</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer, (Production Excellence)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AIA Contract Documents</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, GCP, MongoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27b382a0dd9b7c72</t>
+          <t>https://www.indeed.com/viewjob?jk=f706322313ef04c9</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Solution Engineer - Data Engineering Specialist - Bilingual (Spanish)</t>
+          <t>Senior Software Engineer (Full stack)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>People People</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, PostgreSQL, CI/CD, CodeBuild</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a26823ec6dae45</t>
+          <t>https://www.indeed.com/viewjob?jk=7430c49b9feec362</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Python Developer (Cloud – GCP/Azure) (Remote)</t>
+          <t>Senior Machine Learning Engineer, Trust &amp; Safety</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,15 +3146,295 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kubernetes, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb78589d2a39e4df</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Entry-level Moment Google Contact Center Developer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26650088972ec91e</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>AIA Contract Documents</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27b382a0dd9b7c72</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>API Architect</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51953c5002c89827</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Solution Engineer - Data Engineering Specialist - Bilingual (Spanish)</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92a26823ec6dae45</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java [Hybrid]</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f21cb7010e5a8a63</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java [Hybrid]</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a6d4850de30c8ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java [Hybrid]</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc22d977c810f0a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Senior Python Developer (Cloud – GCP/Azure) (Remote)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Bentonville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
           <t>AWS, ECS, RDS, Azure, GCP, Spark, PySpark, Scala, Airflow, Git</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c4f629c97031e8ed</t>
         </is>

--- a/results/job_matches_2026-04-14.xlsx
+++ b/results/job_matches_2026-04-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Salesforce Architect</t>
+          <t>Senior Full Stack Engineer - AI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">KPRMT Global solutions </t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573c4c858dde7f71</t>
+          <t>https://www.indeed.com/viewjob?jk=f2cc2730bd14a3e8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2cc2730bd14a3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=8cba17f74f3a8a87</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>metropolis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cba17f74f3a8a87</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc5289c2eff0fe3</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>metropolis</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc5289c2eff0fe3</t>
+          <t>https://www.indeed.com/viewjob?jk=0db447e4c4e1f04b</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db447e4c4e1f04b</t>
+          <t>https://www.indeed.com/viewjob?jk=b55ea3b297953077</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55ea3b297953077</t>
+          <t>https://www.indeed.com/viewjob?jk=d857667edacbcc1e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>EMR, Redshift, S3, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d857667edacbcc1e</t>
+          <t>https://www.indeed.com/viewjob?jk=7529728374eb4213</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Machine Learning</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>EMR, Redshift, S3, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7529728374eb4213</t>
+          <t>https://www.indeed.com/viewjob?jk=a513718316ea30dd</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a513718316ea30dd</t>
+          <t>https://www.indeed.com/viewjob?jk=43cfe33e6a3659da</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43cfe33e6a3659da</t>
+          <t>https://www.indeed.com/viewjob?jk=620e166ed5473039</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ML Infrastructure/Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620e166ed5473039</t>
+          <t>https://www.indeed.com/viewjob?jk=6121915b4e45790d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ML Infrastructure/Platform Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,112 +1186,112 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6121915b4e45790d</t>
+          <t>https://www.indeed.com/viewjob?jk=25e97510ea5ed940</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Data Engineer - United States</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25e97510ea5ed940</t>
+          <t>https://www.indeed.com/viewjob?jk=04db638500700cb1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Software Engineer 3 - Contingent (contract)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79c136294cfd98fe</t>
+          <t>https://www.indeed.com/viewjob?jk=7051fd3bf67a37ac</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AWS Data Architect (Hybrid)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Signet Jewelers</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Coppell, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, SQS, SNS, API Gateway, IAM, RDS</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0e64cf5300616c</t>
+          <t>https://www.indeed.com/viewjob?jk=72b0fdeb9512d34e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer - United States</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04db638500700cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b78c747cdda3eb</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer 3 - Contingent (contract)</t>
+          <t>Software Development Engineer - Credential API</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7051fd3bf67a37ac</t>
+          <t>https://www.indeed.com/viewjob?jk=88c29ef248c94981</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Computing Architect (Mid-Level or Senior)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>William Blair &amp; Company</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bda91a521ece52f</t>
+          <t>https://www.indeed.com/viewjob?jk=cea3dbea7cb13bbf</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Azure</t>
+          <t>Senior Applications Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=890935458d36553e</t>
+          <t>https://www.indeed.com/viewjob?jk=5622a97c0cb32459</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer II – Big Data / ETL Engineer (Apptio)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>Databricks, BigQuery, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72b0fdeb9512d34e</t>
+          <t>https://www.indeed.com/viewjob?jk=be9de9e1e7dbc172</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Data Reliability Engineer Oncology Analytics</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b78c747cdda3eb</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a8530ac9c848be</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Architect - C2H - Onsite</t>
+          <t>AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>Synergy BIS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, ECS, RDS, PostgreSQL, MySQL, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=087dc81db4c0ead7</t>
+          <t>https://www.indeed.com/viewjob?jk=dbf74cf2b06a65f1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Applications Developer</t>
+          <t>Sys. Integration Sr. Specialist Advisor</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5622a97c0cb32459</t>
+          <t>https://www.indeed.com/viewjob?jk=43e632ec94c82b3b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Credential API</t>
+          <t>Sys. Integration Sr. Specialist Advisor</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c29ef248c94981</t>
+          <t>https://www.indeed.com/viewjob?jk=1aca172869e592e8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Intermediate Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>William Blair &amp; Company</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, S3, Azure, Hadoop, Spark, Dask, Snowflake, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,89 +1651,89 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cea3dbea7cb13bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=2ccec05543d43588</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Engineer II – Big Data / ETL Engineer (Apptio)</t>
+          <t>Data Engineer/Sr Data Engineer (NOT OPEN TO VISA HOLDERS)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Georgia-Pacific</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Redshift, Step Functions, S3, IAM, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be9de9e1e7dbc172</t>
+          <t>https://www.indeed.com/viewjob?jk=f129032e6f84d172</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer Oncology Analytics</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a8530ac9c848be</t>
+          <t>https://www.indeed.com/viewjob?jk=ed57d3552234a972</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AWS Platform Engineer</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Synergy BIS</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1742,11 +1742,11 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, PostgreSQL, MySQL, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbf74cf2b06a65f1</t>
+          <t>https://www.indeed.com/viewjob?jk=a1567499d777de5d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sys. Integration Sr. Specialist Advisor</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,94 +1791,94 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e632ec94c82b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=6177a38e86fbab44</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sys. Integration Sr. Specialist Advisor</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aca172869e592e8</t>
+          <t>https://www.indeed.com/viewjob?jk=f675cb5511b3a92e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>IT Data Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Tempur + Sealy</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Trinity, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Data Factory, Spark, PySpark, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2444333527505cd</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d7106826dcc9d2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Intermediate Machine Learning Data Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Spark, Dask, Snowflake, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ccec05543d43588</t>
+          <t>https://www.indeed.com/viewjob?jk=2722db66dd139366</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer/Sr Data Engineer (NOT OPEN TO VISA HOLDERS)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Georgia-Pacific</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Step Functions, S3, IAM, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f129032e6f84d172</t>
+          <t>https://www.indeed.com/viewjob?jk=02ca8eea8c20d4f1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed57d3552234a972</t>
+          <t>https://www.indeed.com/viewjob?jk=fd62970232a35032</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6177a38e86fbab44</t>
+          <t>https://www.indeed.com/viewjob?jk=e94dc1bfd30ae5f1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2722db66dd139366</t>
+          <t>https://www.indeed.com/viewjob?jk=ffb45764baeec647</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1567499d777de5d</t>
+          <t>https://www.indeed.com/viewjob?jk=93a9ff833b41ef5d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IT Data Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tempur + Sealy</t>
+          <t>Pluto TV</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Trinity, NC, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Spark, PySpark, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,59 +2106,59 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d7106826dcc9d2</t>
+          <t>https://www.indeed.com/viewjob?jk=46f1c7ebf3cba3e3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f675cb5511b3a92e</t>
+          <t>https://www.indeed.com/viewjob?jk=10b40f262a4271a7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
+          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, Azure Cosmos DB, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ca8eea8c20d4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=d78327146c19a784</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,24 +2201,24 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd62970232a35032</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e4bcd62747c894</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e94dc1bfd30ae5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=f8bde7b210d67def</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
+          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffb45764baeec647</t>
+          <t>https://www.indeed.com/viewjob?jk=dd96031899aef8e4</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>JobSPOT</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93a9ff833b41ef5d</t>
+          <t>https://www.indeed.com/viewjob?jk=d30905e392635ceb</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Web Software Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>Mouser Electronics</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Mansfield, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f1c7ebf3cba3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=336c0c1bf86693ef</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Hifi</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b40f262a4271a7</t>
+          <t>https://www.indeed.com/viewjob?jk=7522730840daa67d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Precisely</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, Azure Cosmos DB, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d78327146c19a784</t>
+          <t>https://www.indeed.com/viewjob?jk=27d727c9d934f72b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Tester (Python) - 6254091</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, PySpark, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e4bcd62747c894</t>
+          <t>https://www.indeed.com/viewjob?jk=89141221ea154795</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr Web Software Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mouser Electronics</t>
+          <t>Path Robotics, Inc.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Mansfield, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,67 +2491,67 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=336c0c1bf86693ef</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0c06f03d80ad17</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Senior DevOps Cloud Engineer (Information Technology Subject Matter Expert)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>State of Connecticut</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac2463a9d29a6913</t>
+          <t>https://www.indeed.com/viewjob?jk=d267e859d5950f5a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>RNGD</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8bde7b210d67def</t>
+          <t>https://www.indeed.com/viewjob?jk=f60859d558e50585</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd96031899aef8e4</t>
+          <t>https://www.indeed.com/viewjob?jk=c3fa7b3be8f9a0fb</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JobSPOT</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d30905e392635ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3e97aaf28d0108</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Hifi</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7522730840daa67d</t>
+          <t>https://www.indeed.com/viewjob?jk=410def4f54721f1a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d727c9d934f72b</t>
+          <t>https://www.indeed.com/viewjob?jk=e8c2e004e287ec36</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Tester (Python) - 6254091</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, PySpark, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89141221ea154795</t>
+          <t>https://www.indeed.com/viewjob?jk=b55d3d996d9d61dc</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Path Robotics, Inc.</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0c06f03d80ad17</t>
+          <t>https://www.indeed.com/viewjob?jk=faf1e7e97badd9a1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineering &amp; Operations Specialist</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RNGD</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f60859d558e50585</t>
+          <t>https://www.indeed.com/viewjob?jk=ac0786555ef46de3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Senior Site Reliability Engineer, (Production Excellence)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, MongoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3fa7b3be8f9a0fb</t>
+          <t>https://www.indeed.com/viewjob?jk=f706322313ef04c9</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Senior Machine Learning Engineer, Trust &amp; Safety</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3e97aaf28d0108</t>
+          <t>https://www.indeed.com/viewjob?jk=fb78589d2a39e4df</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>AIA Contract Documents</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410def4f54721f1a</t>
+          <t>https://www.indeed.com/viewjob?jk=27b382a0dd9b7c72</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8c2e004e287ec36</t>
+          <t>https://www.indeed.com/viewjob?jk=f21cb7010e5a8a63</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55d3d996d9d61dc</t>
+          <t>https://www.indeed.com/viewjob?jk=5a6d4850de30c8ce</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf1e7e97badd9a1</t>
+          <t>https://www.indeed.com/viewjob?jk=dc22d977c810f0a5</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Operations Specialist</t>
+          <t>Entry-level Moment Google Contact Center Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0786555ef46de3</t>
+          <t>https://www.indeed.com/viewjob?jk=26650088972ec91e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, (Production Excellence)</t>
+          <t>Solution Engineer - Data Engineering Specialist - Bilingual (Spanish)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,367 +3076,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, MongoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f706322313ef04c9</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full stack)</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>People People</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, PostgreSQL, CI/CD, CodeBuild</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7430c49b9feec362</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer, Trust &amp; Safety</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Match Group</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kubernetes, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb78589d2a39e4df</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Entry-level Moment Google Contact Center Developer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Teaneck, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=26650088972ec91e</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>AIA Contract Documents</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=27b382a0dd9b7c72</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>API Architect</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=51953c5002c89827</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Solution Engineer - Data Engineering Specialist - Bilingual (Spanish)</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=92a26823ec6dae45</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f21cb7010e5a8a63</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6d4850de30c8ce</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dc22d977c810f0a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Senior Python Developer (Cloud – GCP/Azure) (Remote)</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Bentonville, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, PySpark, Scala, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f629c97031e8ed</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-14.xlsx
+++ b/results/job_matches_2026-04-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SentiLink</t>
+          <t>Universal Background Screening</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Azure, GCP</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1963992b9015fbc</t>
+          <t>https://www.indeed.com/viewjob?jk=c305c75d9c817c14</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Data</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>SentiLink</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4341508fe1c04f1</t>
+          <t>https://www.indeed.com/viewjob?jk=e1963992b9015fbc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Sqoop, HBase, Flume, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8855ef540e8dc9e8</t>
+          <t>https://www.indeed.com/viewjob?jk=b4341508fe1c04f1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Parker's Kitchen</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Sqoop, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403fe46aec3ac312</t>
+          <t>https://www.indeed.com/viewjob?jk=8855ef540e8dc9e8</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Parker Management</t>
+          <t>Parker's Kitchen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43381ea07fee685f</t>
+          <t>https://www.indeed.com/viewjob?jk=403fe46aec3ac312</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Engineer, Software</t>
+          <t>Senior Data &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Verint Systems Inc.</t>
+          <t>Parker Management</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c774765a5f06879</t>
+          <t>https://www.indeed.com/viewjob?jk=43381ea07fee685f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data Engineering</t>
+          <t>Engineer, Software</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>Verint Systems Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, S3, Hadoop, Hive, MapReduce, HBase, Spark</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454945ebbe7d1ebf</t>
+          <t>https://www.indeed.com/viewjob?jk=0c774765a5f06879</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Machine Learning</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>EMR, Redshift, S3, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7529728374eb4213</t>
+          <t>https://www.indeed.com/viewjob?jk=a513718316ea30dd</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a513718316ea30dd</t>
+          <t>https://www.indeed.com/viewjob?jk=43cfe33e6a3659da</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43cfe33e6a3659da</t>
+          <t>https://www.indeed.com/viewjob?jk=620e166ed5473039</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ML Infrastructure/Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620e166ed5473039</t>
+          <t>https://www.indeed.com/viewjob?jk=6121915b4e45790d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ML Infrastructure/Platform Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,69 +1151,69 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6121915b4e45790d</t>
+          <t>https://www.indeed.com/viewjob?jk=25e97510ea5ed940</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Data Engineer - United States</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25e97510ea5ed940</t>
+          <t>https://www.indeed.com/viewjob?jk=04db638500700cb1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer - United States</t>
+          <t>Software Engineer 3 - Contingent (contract)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04db638500700cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=7051fd3bf67a37ac</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer 3 - Contingent (contract)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7051fd3bf67a37ac</t>
+          <t>https://www.indeed.com/viewjob?jk=72b0fdeb9512d34e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72b0fdeb9512d34e</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b78c747cdda3eb</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Software Development Engineer - Credential API</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b78c747cdda3eb</t>
+          <t>https://www.indeed.com/viewjob?jk=88c29ef248c94981</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Credential API</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>William Blair &amp; Company</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c29ef248c94981</t>
+          <t>https://www.indeed.com/viewjob?jk=cea3dbea7cb13bbf</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Applications Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>William Blair &amp; Company</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,59 +1406,59 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cea3dbea7cb13bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=5622a97c0cb32459</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Applications Developer</t>
+          <t>Engineer II – Big Data / ETL Engineer (Apptio)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>Databricks, BigQuery, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5622a97c0cb32459</t>
+          <t>https://www.indeed.com/viewjob?jk=be9de9e1e7dbc172</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Engineer II – Big Data / ETL Engineer (Apptio)</t>
+          <t>Data Reliability Engineer Oncology Analytics</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be9de9e1e7dbc172</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a8530ac9c848be</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer Oncology Analytics</t>
+          <t>AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Synergy BIS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, ECS, RDS, PostgreSQL, MySQL, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a8530ac9c848be</t>
+          <t>https://www.indeed.com/viewjob?jk=dbf74cf2b06a65f1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AWS Platform Engineer</t>
+          <t>Sys. Integration Sr. Specialist Advisor</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Synergy BIS</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, PostgreSQL, MySQL, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbf74cf2b06a65f1</t>
+          <t>https://www.indeed.com/viewjob?jk=43e632ec94c82b3b</t>
         </is>
       </c>
     </row>
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e632ec94c82b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=1aca172869e592e8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sys. Integration Sr. Specialist Advisor</t>
+          <t>Intermediate Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, S3, Azure, Hadoop, Spark, Dask, Snowflake, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aca172869e592e8</t>
+          <t>https://www.indeed.com/viewjob?jk=2ccec05543d43588</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Intermediate Machine Learning Data Engineer</t>
+          <t>Data Engineer/Sr Data Engineer (NOT OPEN TO VISA HOLDERS)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>Georgia-Pacific</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Spark, Dask, Snowflake, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Glue, Redshift, Step Functions, S3, IAM, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ccec05543d43588</t>
+          <t>https://www.indeed.com/viewjob?jk=f129032e6f84d172</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer/Sr Data Engineer (NOT OPEN TO VISA HOLDERS)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Georgia-Pacific</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Step Functions, S3, IAM, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f129032e6f84d172</t>
+          <t>https://www.indeed.com/viewjob?jk=ed57d3552234a972</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed57d3552234a972</t>
+          <t>https://www.indeed.com/viewjob?jk=6177a38e86fbab44</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6177a38e86fbab44</t>
+          <t>https://www.indeed.com/viewjob?jk=f675cb5511b3a92e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>IT Data Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Tempur + Sealy</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Trinity, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, Azure, Data Factory, Spark, PySpark, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f675cb5511b3a92e</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d7106826dcc9d2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>IT Data Developer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tempur + Sealy</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Trinity, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Spark, PySpark, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d7106826dcc9d2</t>
+          <t>https://www.indeed.com/viewjob?jk=2722db66dd139366</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2722db66dd139366</t>
+          <t>https://www.indeed.com/viewjob?jk=02ca8eea8c20d4f1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ca8eea8c20d4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=fd62970232a35032</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd62970232a35032</t>
+          <t>https://www.indeed.com/viewjob?jk=e94dc1bfd30ae5f1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e94dc1bfd30ae5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=ffb45764baeec647</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffb45764baeec647</t>
+          <t>https://www.indeed.com/viewjob?jk=93a9ff833b41ef5d</t>
         </is>
       </c>
     </row>
@@ -2048,12 +2048,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>Pluto TV</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93a9ff833b41ef5d</t>
+          <t>https://www.indeed.com/viewjob?jk=46f1c7ebf3cba3e3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f1c7ebf3cba3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=10b40f262a4271a7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, Azure Cosmos DB, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b40f262a4271a7</t>
+          <t>https://www.indeed.com/viewjob?jk=d78327146c19a784</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, Azure Cosmos DB, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d78327146c19a784</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e4bcd62747c894</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e4bcd62747c894</t>
+          <t>https://www.indeed.com/viewjob?jk=f8bde7b210d67def</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8bde7b210d67def</t>
+          <t>https://www.indeed.com/viewjob?jk=dd96031899aef8e4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>JobSPOT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd96031899aef8e4</t>
+          <t>https://www.indeed.com/viewjob?jk=d30905e392635ceb</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>Sr Web Software Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JobSPOT</t>
+          <t>Mouser Electronics</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Mansfield, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d30905e392635ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=336c0c1bf86693ef</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Web Software Developer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mouser Electronics</t>
+          <t>Hifi</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Mansfield, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=336c0c1bf86693ef</t>
+          <t>https://www.indeed.com/viewjob?jk=7522730840daa67d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Hifi</t>
+          <t>Precisely</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7522730840daa67d</t>
+          <t>https://www.indeed.com/viewjob?jk=27d727c9d934f72b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Tester (Python) - 6254091</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, PySpark, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d727c9d934f72b</t>
+          <t>https://www.indeed.com/viewjob?jk=89141221ea154795</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Tester (Python) - 6254091</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Path Robotics, Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, PySpark, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89141221ea154795</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0c06f03d80ad17</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior DevOps Cloud Engineer (Information Technology Subject Matter Expert)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Path Robotics, Inc.</t>
+          <t>State of Connecticut</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0c06f03d80ad17</t>
+          <t>https://www.indeed.com/viewjob?jk=d267e859d5950f5a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer (Information Technology Subject Matter Expert)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>State of Connecticut</t>
+          <t>RNGD</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d267e859d5950f5a</t>
+          <t>https://www.indeed.com/viewjob?jk=f60859d558e50585</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RNGD</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f60859d558e50585</t>
+          <t>https://www.indeed.com/viewjob?jk=c3fa7b3be8f9a0fb</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3fa7b3be8f9a0fb</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3e97aaf28d0108</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3e97aaf28d0108</t>
+          <t>https://www.indeed.com/viewjob?jk=410def4f54721f1a</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410def4f54721f1a</t>
+          <t>https://www.indeed.com/viewjob?jk=e8c2e004e287ec36</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8c2e004e287ec36</t>
+          <t>https://www.indeed.com/viewjob?jk=b55d3d996d9d61dc</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55d3d996d9d61dc</t>
+          <t>https://www.indeed.com/viewjob?jk=faf1e7e97badd9a1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf1e7e97badd9a1</t>
+          <t>https://www.indeed.com/viewjob?jk=eb067c7ee9c6e671</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Operations Specialist</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0786555ef46de3</t>
+          <t>https://www.indeed.com/viewjob?jk=de4543a914df9789</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, (Production Excellence)</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, MongoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f706322313ef04c9</t>
+          <t>https://www.indeed.com/viewjob?jk=f21cb7010e5a8a63</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Trust &amp; Safety</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb78589d2a39e4df</t>
+          <t>https://www.indeed.com/viewjob?jk=5a6d4850de30c8ce</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AIA Contract Documents</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27b382a0dd9b7c72</t>
+          <t>https://www.indeed.com/viewjob?jk=dc22d977c810f0a5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Entry-level Moment Google Contact Center Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21cb7010e5a8a63</t>
+          <t>https://www.indeed.com/viewjob?jk=26650088972ec91e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>AIA Contract Documents</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6d4850de30c8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=27b382a0dd9b7c72</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Senior Machine Learning Engineer, Trust &amp; Safety</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc22d977c810f0a5</t>
+          <t>https://www.indeed.com/viewjob?jk=fb78589d2a39e4df</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Entry-level Moment Google Contact Center Developer</t>
+          <t>Solution Engineer - Data Engineering Specialist - Bilingual (Spanish)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,50 +3041,15 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=26650088972ec91e</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Solution Engineer - Data Engineering Specialist - Bilingual (Spanish)</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=92a26823ec6dae45</t>
         </is>

--- a/results/job_matches_2026-04-14.xlsx
+++ b/results/job_matches_2026-04-14.xlsx
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6177a38e86fbab44</t>
+          <t>https://www.indeed.com/viewjob?jk=a1567499d777de5d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1567499d777de5d</t>
+          <t>https://www.indeed.com/viewjob?jk=6177a38e86fbab44</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IT Data Developer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tempur + Sealy</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Trinity, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Spark, PySpark, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d7106826dcc9d2</t>
+          <t>https://www.indeed.com/viewjob?jk=2722db66dd139366</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>IT Data Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>Tempur + Sealy</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Trinity, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Azure, Data Factory, Spark, PySpark, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2722db66dd139366</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d7106826dcc9d2</t>
         </is>
       </c>
     </row>
@@ -2813,17 +2813,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Senior Machine Learning Engineer, Trust &amp; Safety</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21cb7010e5a8a63</t>
+          <t>https://www.indeed.com/viewjob?jk=fb78589d2a39e4df</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>AIA Contract Documents</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6d4850de30c8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=27b382a0dd9b7c72</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc22d977c810f0a5</t>
+          <t>https://www.indeed.com/viewjob?jk=f21cb7010e5a8a63</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Entry-level Moment Google Contact Center Developer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26650088972ec91e</t>
+          <t>https://www.indeed.com/viewjob?jk=5a6d4850de30c8ce</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>AIA Contract Documents</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27b382a0dd9b7c72</t>
+          <t>https://www.indeed.com/viewjob?jk=dc22d977c810f0a5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Trust &amp; Safety</t>
+          <t>Entry-level Moment Google Contact Center Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb78589d2a39e4df</t>
+          <t>https://www.indeed.com/viewjob?jk=26650088972ec91e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-14.xlsx
+++ b/results/job_matches_2026-04-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Parker's Kitchen</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Sqoop, HBase, Flume, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8855ef540e8dc9e8</t>
+          <t>https://www.indeed.com/viewjob?jk=403fe46aec3ac312</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Parker's Kitchen</t>
+          <t>Parker Management</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -671,59 +671,59 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403fe46aec3ac312</t>
+          <t>https://www.indeed.com/viewjob?jk=43381ea07fee685f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Integration Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Parker Management</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43381ea07fee685f</t>
+          <t>https://www.indeed.com/viewjob?jk=85e3c201f23e6a22</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Engineer, Software</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Verint Systems Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, IAM, Azure, GCP, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c774765a5f06879</t>
+          <t>https://www.indeed.com/viewjob?jk=a52f9c227e61963c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Engineer, Software</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Verint Systems Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83db8f50bcabcd87</t>
+          <t>https://www.indeed.com/viewjob?jk=0c774765a5f06879</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - AI</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2cc2730bd14a3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=83db8f50bcabcd87</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Salesforce Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t xml:space="preserve">KPRMT Global solutions </t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,19 +846,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cba17f74f3a8a87</t>
+          <t>https://www.indeed.com/viewjob?jk=573c4c858dde7f71</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Engineer - AI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>metropolis</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -867,11 +867,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc5289c2eff0fe3</t>
+          <t>https://www.indeed.com/viewjob?jk=f2cc2730bd14a3e8</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db447e4c4e1f04b</t>
+          <t>https://www.indeed.com/viewjob?jk=8cba17f74f3a8a87</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>metropolis</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55ea3b297953077</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc5289c2eff0fe3</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d857667edacbcc1e</t>
+          <t>https://www.indeed.com/viewjob?jk=0db447e4c4e1f04b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a513718316ea30dd</t>
+          <t>https://www.indeed.com/viewjob?jk=b55ea3b297953077</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43cfe33e6a3659da</t>
+          <t>https://www.indeed.com/viewjob?jk=d857667edacbcc1e</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620e166ed5473039</t>
+          <t>https://www.indeed.com/viewjob?jk=a513718316ea30dd</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ML Infrastructure/Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6121915b4e45790d</t>
+          <t>https://www.indeed.com/viewjob?jk=43cfe33e6a3659da</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25e97510ea5ed940</t>
+          <t>https://www.indeed.com/viewjob?jk=620e166ed5473039</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer - United States</t>
+          <t>ML Infrastructure/Platform Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04db638500700cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=6121915b4e45790d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer 3 - Contingent (contract)</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7051fd3bf67a37ac</t>
+          <t>https://www.indeed.com/viewjob?jk=25e97510ea5ed940</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Data Architect (Hybrid)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Signet Jewelers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Coppell, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, SQS, SNS, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72b0fdeb9512d34e</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0e64cf5300616c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b78c747cdda3eb</t>
+          <t>https://www.indeed.com/viewjob?jk=ae18e6a8860be459</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Credential API</t>
+          <t>Data Engineer - United States</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c29ef248c94981</t>
+          <t>https://www.indeed.com/viewjob?jk=04db638500700cb1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer 3 - Contingent (contract)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>William Blair &amp; Company</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cea3dbea7cb13bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=7051fd3bf67a37ac</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Applications Developer</t>
+          <t>Computing Architect (Mid-Level or Senior)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5622a97c0cb32459</t>
+          <t>https://www.indeed.com/viewjob?jk=8bda91a521ece52f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Engineer II – Big Data / ETL Engineer (Apptio)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be9de9e1e7dbc172</t>
+          <t>https://www.indeed.com/viewjob?jk=72b0fdeb9512d34e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer Oncology Analytics</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a8530ac9c848be</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b78c747cdda3eb</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AWS Platform Engineer</t>
+          <t>Data Architect - C2H - Onsite</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Synergy BIS</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, PostgreSQL, MySQL, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbf74cf2b06a65f1</t>
+          <t>https://www.indeed.com/viewjob?jk=087dc81db4c0ead7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sys. Integration Sr. Specialist Advisor</t>
+          <t>Senior Applications Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e632ec94c82b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=5622a97c0cb32459</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sys. Integration Sr. Specialist Advisor</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Frida</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, IAM, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aca172869e592e8</t>
+          <t>https://www.indeed.com/viewjob?jk=8900daeea8c64c35</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Intermediate Machine Learning Data Engineer</t>
+          <t>Software Development Engineer - Credential API</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Spark, Dask, Snowflake, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,89 +1616,89 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ccec05543d43588</t>
+          <t>https://www.indeed.com/viewjob?jk=88c29ef248c94981</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer/Sr Data Engineer (NOT OPEN TO VISA HOLDERS)</t>
+          <t>Engineer II – Big Data / ETL Engineer (Apptio)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Georgia-Pacific</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Step Functions, S3, IAM, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>Databricks, BigQuery, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f129032e6f84d172</t>
+          <t>https://www.indeed.com/viewjob?jk=be9de9e1e7dbc172</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Reliability Engineer Oncology Analytics</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed57d3552234a972</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a8530ac9c848be</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Synergy BIS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1707,11 +1707,11 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, ECS, RDS, PostgreSQL, MySQL, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1567499d777de5d</t>
+          <t>https://www.indeed.com/viewjob?jk=dbf74cf2b06a65f1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sys. Integration Sr. Specialist Advisor</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,59 +1756,59 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6177a38e86fbab44</t>
+          <t>https://www.indeed.com/viewjob?jk=43e632ec94c82b3b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Sys. Integration Sr. Specialist Advisor</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f675cb5511b3a92e</t>
+          <t>https://www.indeed.com/viewjob?jk=1aca172869e592e8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Intermediate Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, S3, Azure, Hadoop, Spark, Dask, Snowflake, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2722db66dd139366</t>
+          <t>https://www.indeed.com/viewjob?jk=2ccec05543d43588</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>IT Data Developer</t>
+          <t>Data Engineer/Sr Data Engineer (NOT OPEN TO VISA HOLDERS)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tempur + Sealy</t>
+          <t>Georgia-Pacific</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Trinity, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Spark, PySpark, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Redshift, Step Functions, S3, IAM, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d7106826dcc9d2</t>
+          <t>https://www.indeed.com/viewjob?jk=f129032e6f84d172</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ca8eea8c20d4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=ed57d3552234a972</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd62970232a35032</t>
+          <t>https://www.indeed.com/viewjob?jk=6177a38e86fbab44</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e94dc1bfd30ae5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=2722db66dd139366</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffb45764baeec647</t>
+          <t>https://www.indeed.com/viewjob?jk=a1567499d777de5d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IT Data Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>Tempur + Sealy</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Trinity, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Spark, PySpark, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,59 +2036,59 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93a9ff833b41ef5d</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d7106826dcc9d2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f1c7ebf3cba3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=f675cb5511b3a92e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b40f262a4271a7</t>
+          <t>https://www.indeed.com/viewjob?jk=7a27a8acf3bc1bc8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, Azure Cosmos DB, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d78327146c19a784</t>
+          <t>https://www.indeed.com/viewjob?jk=02ca8eea8c20d4f1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,24 +2166,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e4bcd62747c894</t>
+          <t>https://www.indeed.com/viewjob?jk=fd62970232a35032</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8bde7b210d67def</t>
+          <t>https://www.indeed.com/viewjob?jk=e94dc1bfd30ae5f1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
+          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd96031899aef8e4</t>
+          <t>https://www.indeed.com/viewjob?jk=ffb45764baeec647</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JobSPOT</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d30905e392635ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=93a9ff833b41ef5d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Web Software Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mouser Electronics</t>
+          <t>Pluto TV</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Mansfield, TX, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=336c0c1bf86693ef</t>
+          <t>https://www.indeed.com/viewjob?jk=46f1c7ebf3cba3e3</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hifi</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7522730840daa67d</t>
+          <t>https://www.indeed.com/viewjob?jk=10b40f262a4271a7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, Azure Cosmos DB, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d727c9d934f72b</t>
+          <t>https://www.indeed.com/viewjob?jk=d78327146c19a784</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Tester (Python) - 6254091</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, PySpark, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89141221ea154795</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e4bcd62747c894</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr Web Software Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Path Robotics, Inc.</t>
+          <t>Mouser Electronics</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Mansfield, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,67 +2456,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0c06f03d80ad17</t>
+          <t>https://www.indeed.com/viewjob?jk=336c0c1bf86693ef</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer (Information Technology Subject Matter Expert)</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>State of Connecticut</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d267e859d5950f5a</t>
+          <t>https://www.indeed.com/viewjob?jk=ac2463a9d29a6913</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RNGD</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f60859d558e50585</t>
+          <t>https://www.indeed.com/viewjob?jk=f8bde7b210d67def</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3fa7b3be8f9a0fb</t>
+          <t>https://www.indeed.com/viewjob?jk=dd96031899aef8e4</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>JobSPOT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3e97aaf28d0108</t>
+          <t>https://www.indeed.com/viewjob?jk=d30905e392635ceb</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Hifi</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410def4f54721f1a</t>
+          <t>https://www.indeed.com/viewjob?jk=7522730840daa67d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Data Tester (Python) - 6254091</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, PySpark, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8c2e004e287ec36</t>
+          <t>https://www.indeed.com/viewjob?jk=89141221ea154795</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Path Robotics, Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55d3d996d9d61dc</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0c06f03d80ad17</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Senior DevOps Cloud Engineer (Information Technology Subject Matter Expert)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>State of Connecticut</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf1e7e97badd9a1</t>
+          <t>https://www.indeed.com/viewjob?jk=d267e859d5950f5a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>RNGD</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb067c7ee9c6e671</t>
+          <t>https://www.indeed.com/viewjob?jk=f60859d558e50585</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4543a914df9789</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3e97aaf28d0108</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Trust &amp; Safety</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb78589d2a39e4df</t>
+          <t>https://www.indeed.com/viewjob?jk=410def4f54721f1a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AIA Contract Documents</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27b382a0dd9b7c72</t>
+          <t>https://www.indeed.com/viewjob?jk=e8c2e004e287ec36</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21cb7010e5a8a63</t>
+          <t>https://www.indeed.com/viewjob?jk=b55d3d996d9d61dc</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6d4850de30c8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=faf1e7e97badd9a1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Senior Geospatial Solutions Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc22d977c810f0a5</t>
+          <t>https://www.indeed.com/viewjob?jk=5f71870dc0f7bc53</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Entry-level Moment Google Contact Center Developer</t>
+          <t>Senior Software Engineer (Full stack)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>People People</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, PostgreSQL, CI/CD, CodeBuild</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26650088972ec91e</t>
+          <t>https://www.indeed.com/viewjob?jk=7430c49b9feec362</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Solution Engineer - Data Engineering Specialist - Bilingual (Spanish)</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,17 +3041,367 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb067c7ee9c6e671</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Salesforce Data Cloud Architect</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>EPAM Systems</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de4543a914df9789</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Entry-level Moment Google Contact Center Developer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26650088972ec91e</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>AIA Contract Documents</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27b382a0dd9b7c72</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>API Architect</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51953c5002c89827</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Solution Engineer - Data Engineering Specialist - Bilingual (Spanish)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=92a26823ec6dae45</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java [Hybrid]</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f21cb7010e5a8a63</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java [Hybrid]</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a6d4850de30c8ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java [Hybrid]</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc22d977c810f0a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Match Group</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kubernetes, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb78589d2a39e4df</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Python Developer (Cloud – GCP/Azure) (Remote)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Bentonville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, PySpark, Scala, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4f629c97031e8ed</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-14.xlsx
+++ b/results/job_matches_2026-04-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,52 +678,52 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Villanova University</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Villanova, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e3c201f23e6a22</t>
+          <t>https://www.indeed.com/viewjob?jk=4acccdfc23951f0d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, IAM, Azure, GCP, Hadoop, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a52f9c227e61963c</t>
+          <t>https://www.indeed.com/viewjob?jk=85e3c201f23e6a22</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Engineer, Software</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Verint Systems Inc.</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c774765a5f06879</t>
+          <t>https://www.indeed.com/viewjob?jk=83db8f50bcabcd87</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Full Stack Engineer - AI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83db8f50bcabcd87</t>
+          <t>https://www.indeed.com/viewjob?jk=f2cc2730bd14a3e8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Salesforce Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">KPRMT Global solutions </t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,19 +846,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573c4c858dde7f71</t>
+          <t>https://www.indeed.com/viewjob?jk=8cba17f74f3a8a87</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>metropolis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -867,11 +867,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2cc2730bd14a3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc5289c2eff0fe3</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cba17f74f3a8a87</t>
+          <t>https://www.indeed.com/viewjob?jk=0db447e4c4e1f04b</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>metropolis</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc5289c2eff0fe3</t>
+          <t>https://www.indeed.com/viewjob?jk=b55ea3b297953077</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db447e4c4e1f04b</t>
+          <t>https://www.indeed.com/viewjob?jk=a513718316ea30dd</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55ea3b297953077</t>
+          <t>https://www.indeed.com/viewjob?jk=43cfe33e6a3659da</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d857667edacbcc1e</t>
+          <t>https://www.indeed.com/viewjob?jk=620e166ed5473039</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ML Infrastructure/Platform Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a513718316ea30dd</t>
+          <t>https://www.indeed.com/viewjob?jk=6121915b4e45790d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,42 +1116,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43cfe33e6a3659da</t>
+          <t>https://www.indeed.com/viewjob?jk=25e97510ea5ed940</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620e166ed5473039</t>
+          <t>https://www.indeed.com/viewjob?jk=ae18e6a8860be459</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ML Infrastructure/Platform Engineer</t>
+          <t>Data Engineer - United States</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,102 +1196,102 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6121915b4e45790d</t>
+          <t>https://www.indeed.com/viewjob?jk=04db638500700cb1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Software Engineer 3 - Contingent (contract)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25e97510ea5ed940</t>
+          <t>https://www.indeed.com/viewjob?jk=7051fd3bf67a37ac</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AWS Data Architect (Hybrid)</t>
+          <t>Mid-Level Engineer, Global</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Signet Jewelers</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Coppell, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, SQS, SNS, API Gateway, IAM, RDS</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0e64cf5300616c</t>
+          <t>https://www.indeed.com/viewjob?jk=9e006537abb3ec5c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae18e6a8860be459</t>
+          <t>https://www.indeed.com/viewjob?jk=5c70a1cb7dff6fb6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer - United States</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04db638500700cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=3de9b476cdbf12e9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer 3 - Contingent (contract)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7051fd3bf67a37ac</t>
+          <t>https://www.indeed.com/viewjob?jk=72b0fdeb9512d34e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Computing Architect (Mid-Level or Senior)</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bda91a521ece52f</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b78c747cdda3eb</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Frida</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72b0fdeb9512d34e</t>
+          <t>https://www.indeed.com/viewjob?jk=8900daeea8c64c35</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Software Development Engineer - Credential API</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b78c747cdda3eb</t>
+          <t>https://www.indeed.com/viewjob?jk=88c29ef248c94981</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Architect - C2H - Onsite</t>
+          <t>Senior Applications Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,112 +1501,112 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=087dc81db4c0ead7</t>
+          <t>https://www.indeed.com/viewjob?jk=5622a97c0cb32459</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Applications Developer</t>
+          <t>Engineer II – Big Data / ETL Engineer (Apptio)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>Databricks, BigQuery, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5622a97c0cb32459</t>
+          <t>https://www.indeed.com/viewjob?jk=be9de9e1e7dbc172</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Reliability Engineer Oncology Analytics</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Frida</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8900daeea8c64c35</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a8530ac9c848be</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Credential API</t>
+          <t>AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Synergy BIS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, ECS, RDS, PostgreSQL, MySQL, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c29ef248c94981</t>
+          <t>https://www.indeed.com/viewjob?jk=dbf74cf2b06a65f1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Engineer II – Big Data / ETL Engineer (Apptio)</t>
+          <t>Sys. Integration Sr. Specialist Advisor</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,42 +1641,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be9de9e1e7dbc172</t>
+          <t>https://www.indeed.com/viewjob?jk=43e632ec94c82b3b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer Oncology Analytics</t>
+          <t>Intermediate Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, S3, Azure, Hadoop, Spark, Dask, Snowflake, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a8530ac9c848be</t>
+          <t>https://www.indeed.com/viewjob?jk=2ccec05543d43588</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AWS Platform Engineer</t>
+          <t>Data Engineer/Sr Data Engineer (NOT OPEN TO VISA HOLDERS)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Synergy BIS</t>
+          <t>Georgia-Pacific</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, PostgreSQL, MySQL, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, Redshift, Step Functions, S3, IAM, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbf74cf2b06a65f1</t>
+          <t>https://www.indeed.com/viewjob?jk=f129032e6f84d172</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sys. Integration Sr. Specialist Advisor</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e632ec94c82b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=ed57d3552234a972</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sys. Integration Sr. Specialist Advisor</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,19 +1791,19 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aca172869e592e8</t>
+          <t>https://www.indeed.com/viewjob?jk=6177a38e86fbab44</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Intermediate Machine Learning Data Engineer</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Spark, Dask, Snowflake, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ccec05543d43588</t>
+          <t>https://www.indeed.com/viewjob?jk=a1567499d777de5d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer/Sr Data Engineer (NOT OPEN TO VISA HOLDERS)</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Georgia-Pacific</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Step Functions, S3, IAM, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f129032e6f84d172</t>
+          <t>https://www.indeed.com/viewjob?jk=f675cb5511b3a92e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,77 +1886,77 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed57d3552234a972</t>
+          <t>https://www.indeed.com/viewjob?jk=2722db66dd139366</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6177a38e86fbab44</t>
+          <t>https://www.indeed.com/viewjob?jk=7a27a8acf3bc1bc8</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,19 +1966,19 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2722db66dd139366</t>
+          <t>https://www.indeed.com/viewjob?jk=02ca8eea8c20d4f1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1987,11 +1987,11 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1567499d777de5d</t>
+          <t>https://www.indeed.com/viewjob?jk=fd62970232a35032</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>IT Data Developer</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tempur + Sealy</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Trinity, NC, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Spark, PySpark, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,59 +2036,59 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d7106826dcc9d2</t>
+          <t>https://www.indeed.com/viewjob?jk=e94dc1bfd30ae5f1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f675cb5511b3a92e</t>
+          <t>https://www.indeed.com/viewjob?jk=ffb45764baeec647</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a27a8acf3bc1bc8</t>
+          <t>https://www.indeed.com/viewjob?jk=93a9ff833b41ef5d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Pluto TV</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
+          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ca8eea8c20d4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=46f1c7ebf3cba3e3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd62970232a35032</t>
+          <t>https://www.indeed.com/viewjob?jk=10b40f262a4271a7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, Azure Cosmos DB, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e94dc1bfd30ae5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=d78327146c19a784</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffb45764baeec647</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e4bcd62747c894</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93a9ff833b41ef5d</t>
+          <t>https://www.indeed.com/viewjob?jk=f8bde7b210d67def</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f1c7ebf3cba3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=dd96031899aef8e4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>JobSPOT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b40f262a4271a7</t>
+          <t>https://www.indeed.com/viewjob?jk=d30905e392635ceb</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr Web Software Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Mouser Electronics</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Mansfield, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, Azure Cosmos DB, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d78327146c19a784</t>
+          <t>https://www.indeed.com/viewjob?jk=336c0c1bf86693ef</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Hifi</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,42 +2411,42 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e4bcd62747c894</t>
+          <t>https://www.indeed.com/viewjob?jk=7522730840daa67d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Web Software Developer</t>
+          <t>Data Tester (Python) - 6254091</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mouser Electronics</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Mansfield, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, PySpark, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=336c0c1bf86693ef</t>
+          <t>https://www.indeed.com/viewjob?jk=89141221ea154795</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Path Robotics, Inc.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,67 +2491,67 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac2463a9d29a6913</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0c06f03d80ad17</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
+          <t>Senior DevOps Cloud Engineer (Information Technology Subject Matter Expert)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>State of Connecticut</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8bde7b210d67def</t>
+          <t>https://www.indeed.com/viewjob?jk=d267e859d5950f5a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>RNGD</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd96031899aef8e4</t>
+          <t>https://www.indeed.com/viewjob?jk=f60859d558e50585</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JobSPOT</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d30905e392635ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3e97aaf28d0108</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Hifi</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7522730840daa67d</t>
+          <t>https://www.indeed.com/viewjob?jk=410def4f54721f1a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Tester (Python) - 6254091</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, PySpark, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89141221ea154795</t>
+          <t>https://www.indeed.com/viewjob?jk=e8c2e004e287ec36</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Path Robotics, Inc.</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0c06f03d80ad17</t>
+          <t>https://www.indeed.com/viewjob?jk=b55d3d996d9d61dc</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer (Information Technology Subject Matter Expert)</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>State of Connecticut</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d267e859d5950f5a</t>
+          <t>https://www.indeed.com/viewjob?jk=faf1e7e97badd9a1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer ( Java)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RNGD</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Decatur, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f60859d558e50585</t>
+          <t>https://www.indeed.com/viewjob?jk=338db949c564e874</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Security Specialist Senior</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3e97aaf28d0108</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7897b7e4bad68e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410def4f54721f1a</t>
+          <t>https://www.indeed.com/viewjob?jk=eb067c7ee9c6e671</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8c2e004e287ec36</t>
+          <t>https://www.indeed.com/viewjob?jk=de4543a914df9789</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55d3d996d9d61dc</t>
+          <t>https://www.indeed.com/viewjob?jk=f21cb7010e5a8a63</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf1e7e97badd9a1</t>
+          <t>https://www.indeed.com/viewjob?jk=5a6d4850de30c8ce</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Geospatial Solutions Architect</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f71870dc0f7bc53</t>
+          <t>https://www.indeed.com/viewjob?jk=dc22d977c810f0a5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full stack)</t>
+          <t>Entry-level Moment Google Contact Center Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>People People</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, PostgreSQL, CI/CD, CodeBuild</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7430c49b9feec362</t>
+          <t>https://www.indeed.com/viewjob?jk=26650088972ec91e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>AIA Contract Documents</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb067c7ee9c6e671</t>
+          <t>https://www.indeed.com/viewjob?jk=27b382a0dd9b7c72</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Senior Machine Learning Engineer, Trust &amp; Safety</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4543a914df9789</t>
+          <t>https://www.indeed.com/viewjob?jk=fb78589d2a39e4df</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Entry-level Moment Google Contact Center Developer</t>
+          <t>Solution Engineer - Data Engineering Specialist - Bilingual (Spanish)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26650088972ec91e</t>
+          <t>https://www.indeed.com/viewjob?jk=92a26823ec6dae45</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Geospatial Solutions Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>AIA Contract Documents</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,262 +3146,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27b382a0dd9b7c72</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>API Architect</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=51953c5002c89827</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Solution Engineer - Data Engineering Specialist - Bilingual (Spanish)</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=92a26823ec6dae45</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f21cb7010e5a8a63</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6d4850de30c8ce</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dc22d977c810f0a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer, Trust &amp; Safety</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Match Group</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kubernetes, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb78589d2a39e4df</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior Python Developer (Cloud – GCP/Azure) (Remote)</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Bentonville, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, PySpark, Scala, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f629c97031e8ed</t>
+          <t>https://www.indeed.com/viewjob?jk=5f71870dc0f7bc53</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-14.xlsx
+++ b/results/job_matches_2026-04-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer - (US - Remote)</t>
+          <t>AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>TargetPath Solutions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS, IAM</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03406469e62daa61</t>
+          <t>https://www.indeed.com/viewjob?jk=ddaefa90999433c3</t>
         </is>
       </c>
     </row>
@@ -538,95 +538,95 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>AI/ML Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SentiLink</t>
+          <t>Marvell Technology</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Azure, GCP</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1963992b9015fbc</t>
+          <t>https://www.indeed.com/viewjob?jk=db6fecac436797a9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Data</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>AmeriLife</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4341508fe1c04f1</t>
+          <t>https://www.indeed.com/viewjob?jk=d10f6b2d0d1b341d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Integration Engineer</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Parker's Kitchen</t>
+          <t>SentiLink</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403fe46aec3ac312</t>
+          <t>https://www.indeed.com/viewjob?jk=e1963992b9015fbc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Integration Engineer</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Parker Management</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43381ea07fee685f</t>
+          <t>https://www.indeed.com/viewjob?jk=b4341508fe1c04f1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Data &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Villanova University</t>
+          <t>Parker's Kitchen</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Villanova, PA, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,169 +696,169 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4acccdfc23951f0d</t>
+          <t>https://www.indeed.com/viewjob?jk=403fe46aec3ac312</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Data &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Parker Management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e3c201f23e6a22</t>
+          <t>https://www.indeed.com/viewjob?jk=43381ea07fee685f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Villanova University</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Villanova, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83db8f50bcabcd87</t>
+          <t>https://www.indeed.com/viewjob?jk=4acccdfc23951f0d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - AI</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2cc2730bd14a3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=85e3c201f23e6a22</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Systems Operations Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>C WATKINS &amp; ASSOCIATES</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cba17f74f3a8a87</t>
+          <t>https://www.indeed.com/viewjob?jk=2f30f60cc3c36e72</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Engineer - AI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>metropolis</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -867,11 +867,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc5289c2eff0fe3</t>
+          <t>https://www.indeed.com/viewjob?jk=f2cc2730bd14a3e8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db447e4c4e1f04b</t>
+          <t>https://www.indeed.com/viewjob?jk=a513718316ea30dd</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55ea3b297953077</t>
+          <t>https://www.indeed.com/viewjob?jk=43cfe33e6a3659da</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a513718316ea30dd</t>
+          <t>https://www.indeed.com/viewjob?jk=620e166ed5473039</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ML Infrastructure/Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43cfe33e6a3659da</t>
+          <t>https://www.indeed.com/viewjob?jk=6121915b4e45790d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620e166ed5473039</t>
+          <t>https://www.indeed.com/viewjob?jk=8cba17f74f3a8a87</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ML Infrastructure/Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>metropolis</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6121915b4e45790d</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc5289c2eff0fe3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,104 +1116,104 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25e97510ea5ed940</t>
+          <t>https://www.indeed.com/viewjob?jk=0db447e4c4e1f04b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae18e6a8860be459</t>
+          <t>https://www.indeed.com/viewjob?jk=b55ea3b297953077</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer - United States</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04db638500700cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=25e97510ea5ed940</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer 3 - Contingent (contract)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,104 +1221,104 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7051fd3bf67a37ac</t>
+          <t>https://www.indeed.com/viewjob?jk=ae18e6a8860be459</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mid-Level Engineer, Global</t>
+          <t>Data Engineer - United States</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e006537abb3ec5c</t>
+          <t>https://www.indeed.com/viewjob?jk=04db638500700cb1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Software Engineer 3 - Contingent (contract)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c70a1cb7dff6fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=7051fd3bf67a37ac</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de9b476cdbf12e9</t>
+          <t>https://www.indeed.com/viewjob?jk=15a32bf71ba33ffa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72b0fdeb9512d34e</t>
+          <t>https://www.indeed.com/viewjob?jk=4d3db28285f41c46</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b78c747cdda3eb</t>
+          <t>https://www.indeed.com/viewjob?jk=3989068a8778fb79</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Mid-Level Engineer, Global</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Frida</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8900daeea8c64c35</t>
+          <t>https://www.indeed.com/viewjob?jk=9e006537abb3ec5c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Credential API</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c29ef248c94981</t>
+          <t>https://www.indeed.com/viewjob?jk=5c70a1cb7dff6fb6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Applications Developer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,77 +1501,77 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5622a97c0cb32459</t>
+          <t>https://www.indeed.com/viewjob?jk=3de9b476cdbf12e9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Engineer II – Big Data / ETL Engineer (Apptio)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be9de9e1e7dbc172</t>
+          <t>https://www.indeed.com/viewjob?jk=72b0fdeb9512d34e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer Oncology Analytics</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a8530ac9c848be</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b78c747cdda3eb</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AWS Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Synergy BIS</t>
+          <t>Frida</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, PostgreSQL, MySQL, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbf74cf2b06a65f1</t>
+          <t>https://www.indeed.com/viewjob?jk=8900daeea8c64c35</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sys. Integration Sr. Specialist Advisor</t>
+          <t>Software Development Engineer - Credential API</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e632ec94c82b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=88c29ef248c94981</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Intermediate Machine Learning Data Engineer</t>
+          <t>Senior Applications Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Spark, Dask, Snowflake, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,102 +1686,102 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ccec05543d43588</t>
+          <t>https://www.indeed.com/viewjob?jk=5622a97c0cb32459</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer/Sr Data Engineer (NOT OPEN TO VISA HOLDERS)</t>
+          <t>Engineer II – Big Data / ETL Engineer (Apptio)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Georgia-Pacific</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Step Functions, S3, IAM, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>Databricks, BigQuery, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f129032e6f84d172</t>
+          <t>https://www.indeed.com/viewjob?jk=be9de9e1e7dbc172</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Reliability Engineer Oncology Analytics</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed57d3552234a972</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a8530ac9c848be</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sys. Integration Sr. Specialist Advisor</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,59 +1791,59 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6177a38e86fbab44</t>
+          <t>https://www.indeed.com/viewjob?jk=43e632ec94c82b3b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Sr Mgr Data Engineering</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1567499d777de5d</t>
+          <t>https://www.indeed.com/viewjob?jk=03e707506ab6122a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Intermediate Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, S3, Azure, Hadoop, Spark, Dask, Snowflake, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f675cb5511b3a92e</t>
+          <t>https://www.indeed.com/viewjob?jk=2ccec05543d43588</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Data Engineer/Sr Data Engineer (NOT OPEN TO VISA HOLDERS)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>Georgia-Pacific</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, Redshift, Step Functions, S3, IAM, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,137 +1896,137 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2722db66dd139366</t>
+          <t>https://www.indeed.com/viewjob?jk=f129032e6f84d172</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a27a8acf3bc1bc8</t>
+          <t>https://www.indeed.com/viewjob?jk=ed57d3552234a972</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Consultant - Data Management (copy)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Beghou Consulting</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ca8eea8c20d4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=d1aec6c41726ff12</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Consultant - Data Management</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Beghou Consulting</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd62970232a35032</t>
+          <t>https://www.indeed.com/viewjob?jk=bb7f4eae35304f9f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e94dc1bfd30ae5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=6177a38e86fbab44</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffb45764baeec647</t>
+          <t>https://www.indeed.com/viewjob?jk=a1567499d777de5d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93a9ff833b41ef5d</t>
+          <t>https://www.indeed.com/viewjob?jk=f675cb5511b3a92e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f1c7ebf3cba3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=2722db66dd139366</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b40f262a4271a7</t>
+          <t>https://www.indeed.com/viewjob?jk=7a27a8acf3bc1bc8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, Azure Cosmos DB, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d78327146c19a784</t>
+          <t>https://www.indeed.com/viewjob?jk=ffb45764baeec647</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e4bcd62747c894</t>
+          <t>https://www.indeed.com/viewjob?jk=02ca8eea8c20d4f1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8bde7b210d67def</t>
+          <t>https://www.indeed.com/viewjob?jk=93a9ff833b41ef5d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Pluto TV</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd96031899aef8e4</t>
+          <t>https://www.indeed.com/viewjob?jk=46f1c7ebf3cba3e3</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JobSPOT</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d30905e392635ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=10b40f262a4271a7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr Web Software Developer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mouser Electronics</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mansfield, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
+          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, Azure Cosmos DB, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=336c0c1bf86693ef</t>
+          <t>https://www.indeed.com/viewjob?jk=d78327146c19a784</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Hifi</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,42 +2411,42 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7522730840daa67d</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e4bcd62747c894</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Tester (Python) - 6254091</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, PySpark, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89141221ea154795</t>
+          <t>https://www.indeed.com/viewjob?jk=fd62970232a35032</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Path Robotics, Inc.</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,67 +2491,67 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0c06f03d80ad17</t>
+          <t>https://www.indeed.com/viewjob?jk=e94dc1bfd30ae5f1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer (Information Technology Subject Matter Expert)</t>
+          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>State of Connecticut</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d267e859d5950f5a</t>
+          <t>https://www.indeed.com/viewjob?jk=f8bde7b210d67def</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RNGD</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f60859d558e50585</t>
+          <t>https://www.indeed.com/viewjob?jk=dd96031899aef8e4</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>JobSPOT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3e97aaf28d0108</t>
+          <t>https://www.indeed.com/viewjob?jk=d30905e392635ceb</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Sr Web Software Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Mouser Electronics</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Mansfield, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410def4f54721f1a</t>
+          <t>https://www.indeed.com/viewjob?jk=336c0c1bf86693ef</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Hifi</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8c2e004e287ec36</t>
+          <t>https://www.indeed.com/viewjob?jk=7522730840daa67d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Senior DevOps Cloud Engineer (Information Technology Subject Matter Expert)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>State of Connecticut</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55d3d996d9d61dc</t>
+          <t>https://www.indeed.com/viewjob?jk=d267e859d5950f5a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>RNGD</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf1e7e97badd9a1</t>
+          <t>https://www.indeed.com/viewjob?jk=f60859d558e50585</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Java)</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Decatur, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338db949c564e874</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3e97aaf28d0108</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Security Specialist Senior</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7897b7e4bad68e</t>
+          <t>https://www.indeed.com/viewjob?jk=410def4f54721f1a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb067c7ee9c6e671</t>
+          <t>https://www.indeed.com/viewjob?jk=e8c2e004e287ec36</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4543a914df9789</t>
+          <t>https://www.indeed.com/viewjob?jk=b55d3d996d9d61dc</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21cb7010e5a8a63</t>
+          <t>https://www.indeed.com/viewjob?jk=faf1e7e97badd9a1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Data Tester (Python) - 6254091</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, PySpark, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6d4850de30c8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=89141221ea154795</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Path Robotics, Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc22d977c810f0a5</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0c06f03d80ad17</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Entry-level Moment Google Contact Center Developer</t>
+          <t>Senior Software Engineer (AI Enablement)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26650088972ec91e</t>
+          <t>https://www.indeed.com/viewjob?jk=48c5c7e7de56c6fb</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Security Specialist Senior</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>AIA Contract Documents</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, RDS, Azure, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27b382a0dd9b7c72</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7897b7e4bad68e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Trust &amp; Safety</t>
+          <t>Senior Software Engineer ( Java)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Decatur, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb78589d2a39e4df</t>
+          <t>https://www.indeed.com/viewjob?jk=338db949c564e874</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Solution Engineer - Data Engineering Specialist - Bilingual (Spanish)</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a26823ec6dae45</t>
+          <t>https://www.indeed.com/viewjob?jk=eb067c7ee9c6e671</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Geospatial Solutions Architect</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,15 +3146,295 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de4543a914df9789</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java [Hybrid]</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f21cb7010e5a8a63</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java [Hybrid]</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a6d4850de30c8ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java [Hybrid]</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc22d977c810f0a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Entry-level Moment Google Contact Center Developer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26650088972ec91e</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>AIA Contract Documents</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27b382a0dd9b7c72</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Solution Engineer - Data Engineering Specialist - Bilingual (Spanish)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92a26823ec6dae45</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Match Group</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kubernetes, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb78589d2a39e4df</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Senior Geospatial Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>American business solutions inc</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
           <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5f71870dc0f7bc53</t>
         </is>

--- a/results/job_matches_2026-04-14.xlsx
+++ b/results/job_matches_2026-04-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,87 +468,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TargetPath Solutions</t>
+          <t>Universal Background Screening</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddaefa90999433c3</t>
+          <t>https://www.indeed.com/viewjob?jk=c305c75d9c817c14</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Remote)</t>
+          <t>AI/ML Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Universal Background Screening</t>
+          <t>Marvell Technology</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c305c75d9c817c14</t>
+          <t>https://www.indeed.com/viewjob?jk=db6fecac436797a9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI/ML Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Marvell Technology</t>
+          <t>AmeriLife</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Kafka</t>
+          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db6fecac436797a9</t>
+          <t>https://www.indeed.com/viewjob?jk=d10f6b2d0d1b341d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AmeriLife</t>
+          <t>SentiLink</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d10f6b2d0d1b341d</t>
+          <t>https://www.indeed.com/viewjob?jk=e1963992b9015fbc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SentiLink</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Azure, GCP</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1963992b9015fbc</t>
+          <t>https://www.indeed.com/viewjob?jk=b4341508fe1c04f1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Data</t>
+          <t>Senior Data &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Parker's Kitchen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4341508fe1c04f1</t>
+          <t>https://www.indeed.com/viewjob?jk=403fe46aec3ac312</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Integration Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Parker's Kitchen</t>
+          <t>Villanova University</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Villanova, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,99 +696,99 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403fe46aec3ac312</t>
+          <t>https://www.indeed.com/viewjob?jk=4acccdfc23951f0d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Integration Engineer</t>
+          <t>Systems Operations Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Parker Management</t>
+          <t>C WATKINS &amp; ASSOCIATES</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43381ea07fee685f</t>
+          <t>https://www.indeed.com/viewjob?jk=2f30f60cc3c36e72</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Villanova University</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Villanova, PA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4acccdfc23951f0d</t>
+          <t>https://www.indeed.com/viewjob?jk=a513718316ea30dd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e3c201f23e6a22</t>
+          <t>https://www.indeed.com/viewjob?jk=43cfe33e6a3659da</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Systems Operations Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C WATKINS &amp; ASSOCIATES</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f30f60cc3c36e72</t>
+          <t>https://www.indeed.com/viewjob?jk=620e166ed5473039</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - AI</t>
+          <t>ML Infrastructure/Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2cc2730bd14a3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=6121915b4e45790d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,159 +916,159 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a513718316ea30dd</t>
+          <t>https://www.indeed.com/viewjob?jk=ae18e6a8860be459</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - United States</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43cfe33e6a3659da</t>
+          <t>https://www.indeed.com/viewjob?jk=04db638500700cb1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer 3 - Contingent (contract)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620e166ed5473039</t>
+          <t>https://www.indeed.com/viewjob?jk=7051fd3bf67a37ac</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ML Infrastructure/Platform Engineer</t>
+          <t>Mid-Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6121915b4e45790d</t>
+          <t>https://www.indeed.com/viewjob?jk=c717630a440c614c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cba17f74f3a8a87</t>
+          <t>https://www.indeed.com/viewjob?jk=15a32bf71ba33ffa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>metropolis</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1077,33 +1077,33 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc5289c2eff0fe3</t>
+          <t>https://www.indeed.com/viewjob?jk=4d3db28285f41c46</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1112,98 +1112,98 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db447e4c4e1f04b</t>
+          <t>https://www.indeed.com/viewjob?jk=3989068a8778fb79</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55ea3b297953077</t>
+          <t>https://www.indeed.com/viewjob?jk=5c70a1cb7dff6fb6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25e97510ea5ed940</t>
+          <t>https://www.indeed.com/viewjob?jk=3de9b476cdbf12e9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1213,50 +1213,50 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae18e6a8860be459</t>
+          <t>https://www.indeed.com/viewjob?jk=72b0fdeb9512d34e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer - United States</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,59 +1266,59 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04db638500700cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b78c747cdda3eb</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer 3 - Contingent (contract)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Frida</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7051fd3bf67a37ac</t>
+          <t>https://www.indeed.com/viewjob?jk=8900daeea8c64c35</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Software Development Engineer - Credential API</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,42 +1326,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15a32bf71ba33ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=88c29ef248c94981</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Engineer II – Big Data / ETL Engineer (Apptio)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>Databricks, BigQuery, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,102 +1371,102 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d3db28285f41c46</t>
+          <t>https://www.indeed.com/viewjob?jk=be9de9e1e7dbc172</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Data Reliability Engineer Oncology Analytics</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3989068a8778fb79</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a8530ac9c848be</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mid-Level Engineer, Global</t>
+          <t>Sys. Integration Sr. Specialist Advisor</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e006537abb3ec5c</t>
+          <t>https://www.indeed.com/viewjob?jk=43e632ec94c82b3b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Sr Mgr Data Engineering</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c70a1cb7dff6fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=03e707506ab6122a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Beacon, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,19 +1511,19 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de9b476cdbf12e9</t>
+          <t>https://www.indeed.com/viewjob?jk=81ac0513866a1f53</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Intermediate Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1532,11 +1532,11 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, Azure, Hadoop, Spark, Dask, Snowflake, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72b0fdeb9512d34e</t>
+          <t>https://www.indeed.com/viewjob?jk=2ccec05543d43588</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Data Engineer/Sr Data Engineer (NOT OPEN TO VISA HOLDERS)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>Georgia-Pacific</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Glue, Redshift, Step Functions, S3, IAM, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b78c747cdda3eb</t>
+          <t>https://www.indeed.com/viewjob?jk=f129032e6f84d172</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Consultant - Data Management (copy)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Frida</t>
+          <t>Beghou Consulting</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Star Schema</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8900daeea8c64c35</t>
+          <t>https://www.indeed.com/viewjob?jk=d1aec6c41726ff12</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Credential API</t>
+          <t>Consultant - Data Management</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Beghou Consulting</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c29ef248c94981</t>
+          <t>https://www.indeed.com/viewjob?jk=bb7f4eae35304f9f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Applications Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5622a97c0cb32459</t>
+          <t>https://www.indeed.com/viewjob?jk=6177a38e86fbab44</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Engineer II – Big Data / ETL Engineer (Apptio)</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be9de9e1e7dbc172</t>
+          <t>https://www.indeed.com/viewjob?jk=a1567499d777de5d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer Oncology Analytics</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a8530ac9c848be</t>
+          <t>https://www.indeed.com/viewjob?jk=2722db66dd139366</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sys. Integration Sr. Specialist Advisor</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e632ec94c82b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=38299c9de7d6d6a0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr Mgr Data Engineering</t>
+          <t>NetApp Emerging Talent - Entry Level Software Engineer (Cloud Storage)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,207 +1826,207 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e707506ab6122a</t>
+          <t>https://www.indeed.com/viewjob?jk=7e07865da969c4a3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Intermediate Machine Learning Data Engineer</t>
+          <t>Sr. Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Spark, Dask, Snowflake, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Snowflake, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ccec05543d43588</t>
+          <t>https://www.indeed.com/viewjob?jk=745ab30cde1846a7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer/Sr Data Engineer (NOT OPEN TO VISA HOLDERS)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Georgia-Pacific</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Step Functions, S3, IAM, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f129032e6f84d172</t>
+          <t>https://www.indeed.com/viewjob?jk=7a27a8acf3bc1bc8</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed57d3552234a972</t>
+          <t>https://www.indeed.com/viewjob?jk=ffb45764baeec647</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Consultant - Data Management (copy)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Beghou Consulting</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1aec6c41726ff12</t>
+          <t>https://www.indeed.com/viewjob?jk=02ca8eea8c20d4f1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Consultant - Data Management</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Beghou Consulting</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb7f4eae35304f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=93a9ff833b41ef5d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Pluto TV</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6177a38e86fbab44</t>
+          <t>https://www.indeed.com/viewjob?jk=46f1c7ebf3cba3e3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1567499d777de5d</t>
+          <t>https://www.indeed.com/viewjob?jk=10b40f262a4271a7</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, Azure Cosmos DB, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f675cb5511b3a92e</t>
+          <t>https://www.indeed.com/viewjob?jk=d78327146c19a784</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2722db66dd139366</t>
+          <t>https://www.indeed.com/viewjob?jk=fd62970232a35032</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a27a8acf3bc1bc8</t>
+          <t>https://www.indeed.com/viewjob?jk=e94dc1bfd30ae5f1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
+          <t>NetApp Emerging Talent - Software Engineer (Cloud Storage)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffb45764baeec647</t>
+          <t>https://www.indeed.com/viewjob?jk=4b72bdc255bbf6f8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>SRE - Application Support (Batch/Cloud)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>DataSync</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ca8eea8c20d4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=58415ab6bf31526f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93a9ff833b41ef5d</t>
+          <t>https://www.indeed.com/viewjob?jk=f8bde7b210d67def</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f1c7ebf3cba3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=dd96031899aef8e4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Sr Web Software Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Mouser Electronics</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Mansfield, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b40f262a4271a7</t>
+          <t>https://www.indeed.com/viewjob?jk=336c0c1bf86693ef</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Hifi</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, Azure Cosmos DB, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d78327146c19a784</t>
+          <t>https://www.indeed.com/viewjob?jk=7522730840daa67d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Cloud Engineer (Information Technology Subject Matter Expert)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>State of Connecticut</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e4bcd62747c894</t>
+          <t>https://www.indeed.com/viewjob?jk=d267e859d5950f5a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>RNGD</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd62970232a35032</t>
+          <t>https://www.indeed.com/viewjob?jk=f60859d558e50585</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e94dc1bfd30ae5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3e97aaf28d0108</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8bde7b210d67def</t>
+          <t>https://www.indeed.com/viewjob?jk=410def4f54721f1a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd96031899aef8e4</t>
+          <t>https://www.indeed.com/viewjob?jk=e8c2e004e287ec36</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JobSPOT</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d30905e392635ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=b55d3d996d9d61dc</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr Web Software Developer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mouser Electronics</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Mansfield, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=336c0c1bf86693ef</t>
+          <t>https://www.indeed.com/viewjob?jk=faf1e7e97badd9a1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Data Tester (Python) - 6254091</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Hifi</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, PySpark, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7522730840daa67d</t>
+          <t>https://www.indeed.com/viewjob?jk=89141221ea154795</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer (Information Technology Subject Matter Expert)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>State of Connecticut</t>
+          <t>Path Robotics, Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d267e859d5950f5a</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0c06f03d80ad17</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Product Owner</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RNGD</t>
+          <t>Gallagher</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Rolling Meadows, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f60859d558e50585</t>
+          <t>https://www.indeed.com/viewjob?jk=a33815bde90512ef</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Senior Geospatial Solutions Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>S R International Inc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3e97aaf28d0108</t>
+          <t>https://www.indeed.com/viewjob?jk=b4968b1c75b8ea91</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Senior Software Engineer (AI Enablement)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410def4f54721f1a</t>
+          <t>https://www.indeed.com/viewjob?jk=48c5c7e7de56c6fb</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Security Specialist Senior</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8c2e004e287ec36</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7897b7e4bad68e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Senior Specialist - Architecture</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Kafka, Data Modeling, MLOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55d3d996d9d61dc</t>
+          <t>https://www.indeed.com/viewjob?jk=18e84b525a6d6412</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Senior Specialist - Architecture</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Kafka, Data Modeling, MLOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf1e7e97badd9a1</t>
+          <t>https://www.indeed.com/viewjob?jk=ff045a7655f5a9c1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Tester (Python) - 6254091</t>
+          <t>Senior Specialist - Architecture</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, PySpark, ETL, ELT, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Kafka, Data Modeling, MLOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89141221ea154795</t>
+          <t>https://www.indeed.com/viewjob?jk=38d9a99d3fb7e65b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Analytics Engineer, Product</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Path Robotics, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
+          <t>RDS, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0c06f03d80ad17</t>
+          <t>https://www.indeed.com/viewjob?jk=55bfb1f792ebb8b4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AI Enablement)</t>
+          <t>Senior Analytics Engineer, Product</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
+          <t>RDS, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48c5c7e7de56c6fb</t>
+          <t>https://www.indeed.com/viewjob?jk=c3759bc62b11d8fa</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Security Specialist Senior</t>
+          <t>Senior Analytics Engineer, Product</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7897b7e4bad68e</t>
+          <t>https://www.indeed.com/viewjob?jk=24e834cbb69e3e31</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Java)</t>
+          <t>Senior Data Engineer: $150-160,000, MN Based, Hybrid - 2 Days in Office</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>GovDocs</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Decatur, GA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, MongoDB, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338db949c564e874</t>
+          <t>https://www.indeed.com/viewjob?jk=8acefc49a07f2d39</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Senior Software Engineer ( Java)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Decatur, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb067c7ee9c6e671</t>
+          <t>https://www.indeed.com/viewjob?jk=338db949c564e874</t>
         </is>
       </c>
     </row>
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4543a914df9789</t>
+          <t>https://www.indeed.com/viewjob?jk=eb067c7ee9c6e671</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21cb7010e5a8a63</t>
+          <t>https://www.indeed.com/viewjob?jk=de4543a914df9789</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6d4850de30c8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=f21cb7010e5a8a63</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc22d977c810f0a5</t>
+          <t>https://www.indeed.com/viewjob?jk=5a6d4850de30c8ce</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Entry-level Moment Google Contact Center Developer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26650088972ec91e</t>
+          <t>https://www.indeed.com/viewjob?jk=dc22d977c810f0a5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Entry-level Moment Google Contact Center Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AIA Contract Documents</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27b382a0dd9b7c72</t>
+          <t>https://www.indeed.com/viewjob?jk=26650088972ec91e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Solution Engineer - Data Engineering Specialist - Bilingual (Spanish)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>AIA Contract Documents</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a26823ec6dae45</t>
+          <t>https://www.indeed.com/viewjob?jk=27b382a0dd9b7c72</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Trust &amp; Safety</t>
+          <t>Solution Engineer - Data Engineering Specialist - Bilingual (Spanish)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kubernetes, Airflow, Git</t>
+          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb78589d2a39e4df</t>
+          <t>https://www.indeed.com/viewjob?jk=92a26823ec6dae45</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Geospatial Solutions Architect</t>
+          <t>Senior Machine Learning Engineer, Trust &amp; Safety</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,15 +3426,50 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kubernetes, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb78589d2a39e4df</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Senior Geospatial Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>American business solutions inc</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
           <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5f71870dc0f7bc53</t>
         </is>

--- a/results/job_matches_2026-04-14.xlsx
+++ b/results/job_matches_2026-04-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Remote)</t>
+          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Universal Background Screening</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,69 +486,69 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c305c75d9c817c14</t>
+          <t>https://www.indeed.com/viewjob?jk=452922c279cc36e9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI/ML Data Engineer</t>
+          <t>DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Marvell Technology</t>
+          <t>Universal Background Screening</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Kafka</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db6fecac436797a9</t>
+          <t>https://www.indeed.com/viewjob?jk=c305c75d9c817c14</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI/ML Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AmeriLife</t>
+          <t>Marvell Technology</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d10f6b2d0d1b341d</t>
+          <t>https://www.indeed.com/viewjob?jk=db6fecac436797a9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SentiLink</t>
+          <t>AmeriLife</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Azure, GCP</t>
+          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1963992b9015fbc</t>
+          <t>https://www.indeed.com/viewjob?jk=d10f6b2d0d1b341d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Data</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>SentiLink</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4341508fe1c04f1</t>
+          <t>https://www.indeed.com/viewjob?jk=e1963992b9015fbc</t>
         </is>
       </c>
     </row>
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Data Engineer 2026 - US,UK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Villanova University</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Villanova, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,77 +696,77 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4acccdfc23951f0d</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d01fdc4061dd2a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Systems Operations Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>C WATKINS &amp; ASSOCIATES</t>
+          <t>Villanova University</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Villanova, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f30f60cc3c36e72</t>
+          <t>https://www.indeed.com/viewjob?jk=4acccdfc23951f0d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a513718316ea30dd</t>
+          <t>https://www.indeed.com/viewjob?jk=5f9a309f4efa98f8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Systems Operations Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>C WATKINS &amp; ASSOCIATES</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43cfe33e6a3659da</t>
+          <t>https://www.indeed.com/viewjob?jk=2f30f60cc3c36e72</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620e166ed5473039</t>
+          <t>https://www.indeed.com/viewjob?jk=a513718316ea30dd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ML Infrastructure/Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6121915b4e45790d</t>
+          <t>https://www.indeed.com/viewjob?jk=43cfe33e6a3659da</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae18e6a8860be459</t>
+          <t>https://www.indeed.com/viewjob?jk=620e166ed5473039</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer - United States</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04db638500700cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=ae18e6a8860be459</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer 3 - Contingent (contract)</t>
+          <t>Enterprise Architect, Azure</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,69 +976,69 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7051fd3bf67a37ac</t>
+          <t>https://www.indeed.com/viewjob?jk=a406a8e4ff0f952d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mid-Level Data Engineer, Global</t>
+          <t>Software Engineer 3 - Contingent (contract)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c717630a440c614c</t>
+          <t>https://www.indeed.com/viewjob?jk=7051fd3bf67a37ac</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>The Cummings Agency</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15a32bf71ba33ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=91c4fcda77fa7425</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Mid-Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d3db28285f41c46</t>
+          <t>https://www.indeed.com/viewjob?jk=c717630a440c614c</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3989068a8778fb79</t>
+          <t>https://www.indeed.com/viewjob?jk=15a32bf71ba33ffa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c70a1cb7dff6fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=4d3db28285f41c46</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de9b476cdbf12e9</t>
+          <t>https://www.indeed.com/viewjob?jk=3989068a8778fb79</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72b0fdeb9512d34e</t>
+          <t>https://www.indeed.com/viewjob?jk=5c70a1cb7dff6fb6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b78c747cdda3eb</t>
+          <t>https://www.indeed.com/viewjob?jk=3de9b476cdbf12e9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Frida</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8900daeea8c64c35</t>
+          <t>https://www.indeed.com/viewjob?jk=72b0fdeb9512d34e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Credential API</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c29ef248c94981</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b78c747cdda3eb</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Engineer II – Big Data / ETL Engineer (Apptio)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Frida</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>AWS, IAM, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be9de9e1e7dbc172</t>
+          <t>https://www.indeed.com/viewjob?jk=8900daeea8c64c35</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer Oncology Analytics</t>
+          <t>Software Development Engineer - Credential API</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a8530ac9c848be</t>
+          <t>https://www.indeed.com/viewjob?jk=88c29ef248c94981</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sys. Integration Sr. Specialist Advisor</t>
+          <t>Engineer II – Big Data / ETL Engineer (Apptio)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>Databricks, BigQuery, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e632ec94c82b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=be9de9e1e7dbc172</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Mgr Data Engineering</t>
+          <t>Data Reliability Engineer Oncology Analytics</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,104 +1466,104 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e707506ab6122a</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a8530ac9c848be</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sys. Integration Sr. Specialist Advisor</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Beacon, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81ac0513866a1f53</t>
+          <t>https://www.indeed.com/viewjob?jk=43e632ec94c82b3b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Intermediate Machine Learning Data Engineer</t>
+          <t>Sr Mgr Data Engineering</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Spark, Dask, Snowflake, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ccec05543d43588</t>
+          <t>https://www.indeed.com/viewjob?jk=03e707506ab6122a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer/Sr Data Engineer (NOT OPEN TO VISA HOLDERS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Georgia-Pacific</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Beacon, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Step Functions, S3, IAM, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f129032e6f84d172</t>
+          <t>https://www.indeed.com/viewjob?jk=81ac0513866a1f53</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Consultant - Data Management (copy)</t>
+          <t>Intermediate Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Beghou Consulting</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, S3, Azure, Hadoop, Spark, Dask, Snowflake, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1aec6c41726ff12</t>
+          <t>https://www.indeed.com/viewjob?jk=2ccec05543d43588</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Consultant - Data Management</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Beghou Consulting</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb7f4eae35304f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=ef58fd9ad5dd15ff</t>
         </is>
       </c>
     </row>
@@ -2043,17 +2043,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b40f262a4271a7</t>
+          <t>https://www.indeed.com/viewjob?jk=fd62970232a35032</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, Azure Cosmos DB, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d78327146c19a784</t>
+          <t>https://www.indeed.com/viewjob?jk=e94dc1bfd30ae5f1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Senior Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Scala, Databricks Lakehouse, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd62970232a35032</t>
+          <t>https://www.indeed.com/viewjob?jk=a6e81f16ad428334</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Senior Dynatrace Observability Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Core BTS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e94dc1bfd30ae5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=504c2eb153af2545</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NetApp Emerging Talent - Software Engineer (Cloud Storage)</t>
+          <t>Sr. Infrastructure, Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Western Union</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, Cassandra, Splunk, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b72bdc255bbf6f8</t>
+          <t>https://www.indeed.com/viewjob?jk=719c318bdfe0b93a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SRE - Application Support (Batch/Cloud)</t>
+          <t>NetApp Emerging Talent - Software Engineer (Cloud Storage)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DataSync</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58415ab6bf31526f</t>
+          <t>https://www.indeed.com/viewjob?jk=4b72bdc255bbf6f8</t>
         </is>
       </c>
     </row>
@@ -2358,17 +2358,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>2026009 - Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Hifi</t>
+          <t>John Deere</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Moline, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Scala, PostgreSQL, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7522730840daa67d</t>
+          <t>https://www.indeed.com/viewjob?jk=45e1a444de87fc2c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer (Information Technology Subject Matter Expert)</t>
+          <t>Microsoft Modern Work Consultant</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>State of Connecticut</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d267e859d5950f5a</t>
+          <t>https://www.indeed.com/viewjob?jk=11d034c0b8905492</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Cloud Engineer (Information Technology Subject Matter Expert)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>RNGD</t>
+          <t>State of Connecticut</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f60859d558e50585</t>
+          <t>https://www.indeed.com/viewjob?jk=d267e859d5950f5a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>RNGD</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3e97aaf28d0108</t>
+          <t>https://www.indeed.com/viewjob?jk=f60859d558e50585</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410def4f54721f1a</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3e97aaf28d0108</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8c2e004e287ec36</t>
+          <t>https://www.indeed.com/viewjob?jk=410def4f54721f1a</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55d3d996d9d61dc</t>
+          <t>https://www.indeed.com/viewjob?jk=e8c2e004e287ec36</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf1e7e97badd9a1</t>
+          <t>https://www.indeed.com/viewjob?jk=b55d3d996d9d61dc</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Tester (Python) - 6254091</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, PySpark, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89141221ea154795</t>
+          <t>https://www.indeed.com/viewjob?jk=faf1e7e97badd9a1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Tester (Python) - 6254091</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Path Robotics, Inc.</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, PySpark, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0c06f03d80ad17</t>
+          <t>https://www.indeed.com/viewjob?jk=89141221ea154795</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Product Owner</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Gallagher</t>
+          <t>Path Robotics, Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Rolling Meadows, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33815bde90512ef</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0c06f03d80ad17</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Geospatial Solutions Architect</t>
+          <t>Senior Specialist - Architecture</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>S R International Inc</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Kafka, Data Modeling, MLOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4968b1c75b8ea91</t>
+          <t>https://www.indeed.com/viewjob?jk=18e84b525a6d6412</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AI Enablement)</t>
+          <t>Senior Specialist - Architecture</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Kafka, Data Modeling, MLOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48c5c7e7de56c6fb</t>
+          <t>https://www.indeed.com/viewjob?jk=ff045a7655f5a9c1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Security Specialist Senior</t>
+          <t>Senior Specialist - Architecture</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Kafka, Data Modeling, MLOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7897b7e4bad68e</t>
+          <t>https://www.indeed.com/viewjob?jk=38d9a99d3fb7e65b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Specialist - Architecture</t>
+          <t>Senior Analytics Engineer, Product</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Kafka, Data Modeling, MLOps, Docker, Kubernetes</t>
+          <t>RDS, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18e84b525a6d6412</t>
+          <t>https://www.indeed.com/viewjob?jk=55bfb1f792ebb8b4</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Specialist - Architecture</t>
+          <t>Senior Analytics Engineer, Product</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Kafka, Data Modeling, MLOps, Docker, Kubernetes</t>
+          <t>RDS, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff045a7655f5a9c1</t>
+          <t>https://www.indeed.com/viewjob?jk=c3759bc62b11d8fa</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Specialist - Architecture</t>
+          <t>Senior Analytics Engineer, Product</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Kafka, Data Modeling, MLOps, Docker, Kubernetes</t>
+          <t>RDS, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38d9a99d3fb7e65b</t>
+          <t>https://www.indeed.com/viewjob?jk=24e834cbb69e3e31</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Product</t>
+          <t>Senior Geospatial Solutions Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>S R International Inc</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55bfb1f792ebb8b4</t>
+          <t>https://www.indeed.com/viewjob?jk=b4968b1c75b8ea91</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Product</t>
+          <t>Senior Data Engineer: $150-160,000, MN Based, Hybrid - 2 Days in Office</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>GovDocs</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, MongoDB, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3759bc62b11d8fa</t>
+          <t>https://www.indeed.com/viewjob?jk=8acefc49a07f2d39</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Product</t>
+          <t>Senior Software Engineer (AI Enablement)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e834cbb69e3e31</t>
+          <t>https://www.indeed.com/viewjob?jk=48c5c7e7de56c6fb</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer: $150-160,000, MN Based, Hybrid - 2 Days in Office</t>
+          <t>Senior Software Engineer ( Java)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GovDocs</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Decatur, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, MongoDB, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8acefc49a07f2d39</t>
+          <t>https://www.indeed.com/viewjob?jk=338db949c564e874</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Java)</t>
+          <t>Maximo Application Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>RAM Professional Services, LLC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Decatur, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MongoDB, NoSQL, Power BI, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338db949c564e874</t>
+          <t>https://www.indeed.com/viewjob?jk=38110d7445c1f6a3</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Data Product Owner</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>Gallagher</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rolling Meadows, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb067c7ee9c6e671</t>
+          <t>https://www.indeed.com/viewjob?jk=a33815bde90512ef</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Security Specialist Senior</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4543a914df9789</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7897b7e4bad68e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21cb7010e5a8a63</t>
+          <t>https://www.indeed.com/viewjob?jk=eb067c7ee9c6e671</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6d4850de30c8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=de4543a914df9789</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc22d977c810f0a5</t>
+          <t>https://www.indeed.com/viewjob?jk=f21cb7010e5a8a63</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Entry-level Moment Google Contact Center Developer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26650088972ec91e</t>
+          <t>https://www.indeed.com/viewjob?jk=5a6d4850de30c8ce</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AIA Contract Documents</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27b382a0dd9b7c72</t>
+          <t>https://www.indeed.com/viewjob?jk=dc22d977c810f0a5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Solution Engineer - Data Engineering Specialist - Bilingual (Spanish)</t>
+          <t>Entry-level Moment Google Contact Center Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,17 +3391,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a26823ec6dae45</t>
+          <t>https://www.indeed.com/viewjob?jk=26650088972ec91e</t>
         </is>
       </c>
     </row>
@@ -3443,17 +3443,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Geospatial Solutions Architect</t>
+          <t>Solution Engineer - Data Engineering Specialist - Bilingual (Spanish)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,15 +3461,50 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
+          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92a26823ec6dae45</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Geospatial Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>American business solutions inc</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
           <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5f71870dc0f7bc53</t>
         </is>

--- a/results/job_matches_2026-04-14.xlsx
+++ b/results/job_matches_2026-04-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS, Spark</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=452922c279cc36e9</t>
+          <t>https://www.indeed.com/viewjob?jk=4478c55d459f6590</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Remote)</t>
+          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Universal Background Screening</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,69 +521,69 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c305c75d9c817c14</t>
+          <t>https://www.indeed.com/viewjob?jk=452922c279cc36e9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI/ML Data Engineer</t>
+          <t>DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Marvell Technology</t>
+          <t>Universal Background Screening</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Kafka</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db6fecac436797a9</t>
+          <t>https://www.indeed.com/viewjob?jk=c305c75d9c817c14</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI/ML Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AmeriLife</t>
+          <t>Marvell Technology</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d10f6b2d0d1b341d</t>
+          <t>https://www.indeed.com/viewjob?jk=db6fecac436797a9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SentiLink</t>
+          <t>AmeriLife</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Azure, GCP</t>
+          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1963992b9015fbc</t>
+          <t>https://www.indeed.com/viewjob?jk=d10f6b2d0d1b341d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Integration Engineer</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Parker's Kitchen</t>
+          <t>SentiLink</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403fe46aec3ac312</t>
+          <t>https://www.indeed.com/viewjob?jk=e1963992b9015fbc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer 2026 - US,UK</t>
+          <t>Senior Data &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>Parker's Kitchen</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d01fdc4061dd2a</t>
+          <t>https://www.indeed.com/viewjob?jk=403fe46aec3ac312</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Data Engineer 2026 - US,UK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Villanova University</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Villanova, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,77 +731,77 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4acccdfc23951f0d</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d01fdc4061dd2a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Villanova University</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Villanova, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f9a309f4efa98f8</t>
+          <t>https://www.indeed.com/viewjob?jk=4acccdfc23951f0d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Systems Operations Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>C WATKINS &amp; ASSOCIATES</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f30f60cc3c36e72</t>
+          <t>https://www.indeed.com/viewjob?jk=5f9a309f4efa98f8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Systems Operations Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>C WATKINS &amp; ASSOCIATES</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a513718316ea30dd</t>
+          <t>https://www.indeed.com/viewjob?jk=2f30f60cc3c36e72</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43cfe33e6a3659da</t>
+          <t>https://www.indeed.com/viewjob?jk=a513718316ea30dd</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620e166ed5473039</t>
+          <t>https://www.indeed.com/viewjob?jk=43cfe33e6a3659da</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae18e6a8860be459</t>
+          <t>https://www.indeed.com/viewjob?jk=620e166ed5473039</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Azure</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a406a8e4ff0f952d</t>
+          <t>https://www.indeed.com/viewjob?jk=ead7a3e6b1951593</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer 3 - Contingent (contract)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7051fd3bf67a37ac</t>
+          <t>https://www.indeed.com/viewjob?jk=f193a5a41b80d59d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Cummings Agency</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91c4fcda77fa7425</t>
+          <t>https://www.indeed.com/viewjob?jk=ae18e6a8860be459</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mid-Level Data Engineer, Global</t>
+          <t>Enterprise Architect, Azure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,59 +1091,59 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c717630a440c614c</t>
+          <t>https://www.indeed.com/viewjob?jk=a406a8e4ff0f952d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Software Engineer 3 - Contingent (contract)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15a32bf71ba33ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=7051fd3bf67a37ac</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>The Cummings Agency</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d3db28285f41c46</t>
+          <t>https://www.indeed.com/viewjob?jk=91c4fcda77fa7425</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Mid-Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3989068a8778fb79</t>
+          <t>https://www.indeed.com/viewjob?jk=c717630a440c614c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c70a1cb7dff6fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=15a32bf71ba33ffa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de9b476cdbf12e9</t>
+          <t>https://www.indeed.com/viewjob?jk=4d3db28285f41c46</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72b0fdeb9512d34e</t>
+          <t>https://www.indeed.com/viewjob?jk=3989068a8778fb79</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b78c747cdda3eb</t>
+          <t>https://www.indeed.com/viewjob?jk=5c70a1cb7dff6fb6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Frida</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Star Schema</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8900daeea8c64c35</t>
+          <t>https://www.indeed.com/viewjob?jk=3de9b476cdbf12e9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Credential API</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,102 +1406,102 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c29ef248c94981</t>
+          <t>https://www.indeed.com/viewjob?jk=72b0fdeb9512d34e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Engineer II – Big Data / ETL Engineer (Apptio)</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be9de9e1e7dbc172</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b78c747cdda3eb</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer Oncology Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Frida</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, IAM, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a8530ac9c848be</t>
+          <t>https://www.indeed.com/viewjob?jk=8900daeea8c64c35</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sys. Integration Sr. Specialist Advisor</t>
+          <t>Software Development Engineer - Credential API</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e632ec94c82b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=88c29ef248c94981</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Mgr Data Engineering</t>
+          <t>Engineer II – Big Data / ETL Engineer (Apptio)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>Databricks, BigQuery, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e707506ab6122a</t>
+          <t>https://www.indeed.com/viewjob?jk=be9de9e1e7dbc172</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Reliability Engineer Oncology Analytics</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,50 +1563,50 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Beacon, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81ac0513866a1f53</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a8530ac9c848be</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Intermediate Machine Learning Data Engineer</t>
+          <t>Sys. Integration Sr. Specialist Advisor</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Spark, Dask, Snowflake, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ccec05543d43588</t>
+          <t>https://www.indeed.com/viewjob?jk=43e632ec94c82b3b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,94 +1651,94 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef58fd9ad5dd15ff</t>
+          <t>https://www.indeed.com/viewjob?jk=8a0467416d94bb26</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Mgr Data Engineering</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6177a38e86fbab44</t>
+          <t>https://www.indeed.com/viewjob?jk=03e707506ab6122a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Aveva PI Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Hive, Scala, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1567499d777de5d</t>
+          <t>https://www.indeed.com/viewjob?jk=42dd34631f8a4a3a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Beacon, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,77 +1746,77 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2722db66dd139366</t>
+          <t>https://www.indeed.com/viewjob?jk=81ac0513866a1f53</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Intermediate Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD, Git</t>
+          <t>AWS, S3, Azure, Hadoop, Spark, Dask, Snowflake, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38299c9de7d6d6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=2ccec05543d43588</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NetApp Emerging Talent - Entry Level Software Engineer (Cloud Storage)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e07865da969c4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=bf17dcf23ea3201f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Hybrid</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Snowflake, Data Modeling, ETL, CI/CD</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=745ab30cde1846a7</t>
+          <t>https://www.indeed.com/viewjob?jk=ef58fd9ad5dd15ff</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a27a8acf3bc1bc8</t>
+          <t>https://www.indeed.com/viewjob?jk=6177a38e86fbab44</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffb45764baeec647</t>
+          <t>https://www.indeed.com/viewjob?jk=a1567499d777de5d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ca8eea8c20d4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=2722db66dd139366</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>adonis</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93a9ff833b41ef5d</t>
+          <t>https://www.indeed.com/viewjob?jk=e5621c4e542d4639</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f1c7ebf3cba3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=38299c9de7d6d6a0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>NetApp Emerging Talent - Entry Level Software Engineer (Cloud Storage)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd62970232a35032</t>
+          <t>https://www.indeed.com/viewjob?jk=7e07865da969c4a3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Sr. Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Snowflake, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e94dc1bfd30ae5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=745ab30cde1846a7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Databricks Lakehouse, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6e81f16ad428334</t>
+          <t>https://www.indeed.com/viewjob?jk=7a27a8acf3bc1bc8</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Dynatrace Observability Engineer</t>
+          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Core BTS</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=504c2eb153af2545</t>
+          <t>https://www.indeed.com/viewjob?jk=ffb45764baeec647</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Infrastructure, Architect</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Western Union</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Oracle, Cassandra, Splunk, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=719c318bdfe0b93a</t>
+          <t>https://www.indeed.com/viewjob?jk=02ca8eea8c20d4f1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NetApp Emerging Talent - Software Engineer (Cloud Storage)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b72bdc255bbf6f8</t>
+          <t>https://www.indeed.com/viewjob?jk=93a9ff833b41ef5d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Pluto TV</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,14 +2281,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8bde7b210d67def</t>
+          <t>https://www.indeed.com/viewjob?jk=46f1c7ebf3cba3e3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd96031899aef8e4</t>
+          <t>https://www.indeed.com/viewjob?jk=fd62970232a35032</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Web Software Developer</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mouser Electronics</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Mansfield, TX, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=336c0c1bf86693ef</t>
+          <t>https://www.indeed.com/viewjob?jk=e94dc1bfd30ae5f1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026009 - Software Engineer</t>
+          <t>Senior Dynatrace Observability Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>John Deere</t>
+          <t>Core BTS</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Moline, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Scala, PostgreSQL, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e1a444de87fc2c</t>
+          <t>https://www.indeed.com/viewjob?jk=504c2eb153af2545</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Microsoft Modern Work Consultant</t>
+          <t>Sr. Infrastructure, Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Western Union</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, Cassandra, Splunk, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d034c0b8905492</t>
+          <t>https://www.indeed.com/viewjob?jk=719c318bdfe0b93a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer (Information Technology Subject Matter Expert)</t>
+          <t>Senior Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>State of Connecticut</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Databricks Lakehouse, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,102 +2456,102 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d267e859d5950f5a</t>
+          <t>https://www.indeed.com/viewjob?jk=a6e81f16ad428334</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>RNGD</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
+          <t>Hadoop, Hive, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f60859d558e50585</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc89b8593855079</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>NetApp Emerging Talent - Software Engineer (Cloud Storage)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3e97aaf28d0108</t>
+          <t>https://www.indeed.com/viewjob?jk=4b72bdc255bbf6f8</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410def4f54721f1a</t>
+          <t>https://www.indeed.com/viewjob?jk=f8bde7b210d67def</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,59 +2596,59 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8c2e004e287ec36</t>
+          <t>https://www.indeed.com/viewjob?jk=dd96031899aef8e4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>2026009 - Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>John Deere</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Moline, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Scala, PostgreSQL, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55d3d996d9d61dc</t>
+          <t>https://www.indeed.com/viewjob?jk=45e1a444de87fc2c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>MachineMetrics, Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, RDS, Scala, Kafka, PostgreSQL, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf1e7e97badd9a1</t>
+          <t>https://www.indeed.com/viewjob?jk=80173e5fca484063</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Tester (Python) - 6254091</t>
+          <t>Microsoft Modern Work Consultant</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, PySpark, ETL, ELT, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89141221ea154795</t>
+          <t>https://www.indeed.com/viewjob?jk=11d034c0b8905492</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior DevOps Cloud Engineer (Information Technology Subject Matter Expert)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Path Robotics, Inc.</t>
+          <t>State of Connecticut</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0c06f03d80ad17</t>
+          <t>https://www.indeed.com/viewjob?jk=d267e859d5950f5a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Specialist - Architecture</t>
+          <t>Data Tester (Python) - 6254091</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Kafka, Data Modeling, MLOps, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, PySpark, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18e84b525a6d6412</t>
+          <t>https://www.indeed.com/viewjob?jk=89141221ea154795</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Specialist - Architecture</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Path Robotics, Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Kafka, Data Modeling, MLOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff045a7655f5a9c1</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0c06f03d80ad17</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Specialist - Architecture</t>
+          <t>Maximo Application Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>RAM Professional Services, LLC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Kafka, Data Modeling, MLOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MongoDB, NoSQL, Power BI, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38d9a99d3fb7e65b</t>
+          <t>https://www.indeed.com/viewjob?jk=38110d7445c1f6a3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Product</t>
+          <t>Data Product Owner</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Gallagher</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Rolling Meadows, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55bfb1f792ebb8b4</t>
+          <t>https://www.indeed.com/viewjob?jk=a33815bde90512ef</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Product</t>
+          <t>Senior Geospatial Solutions Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>S R International Inc</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3759bc62b11d8fa</t>
+          <t>https://www.indeed.com/viewjob?jk=b4968b1c75b8ea91</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Product</t>
+          <t>Senior Software Engineer (AI Enablement)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e834cbb69e3e31</t>
+          <t>https://www.indeed.com/viewjob?jk=48c5c7e7de56c6fb</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Geospatial Solutions Architect</t>
+          <t>Security Specialist Senior</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>S R International Inc</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, Lambda, RDS, Azure, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4968b1c75b8ea91</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7897b7e4bad68e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer: $150-160,000, MN Based, Hybrid - 2 Days in Office</t>
+          <t>Senior Specialist - Architecture</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GovDocs</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, MongoDB, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Kafka, Data Modeling, MLOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8acefc49a07f2d39</t>
+          <t>https://www.indeed.com/viewjob?jk=18e84b525a6d6412</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AI Enablement)</t>
+          <t>Senior Specialist - Architecture</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Kafka, Data Modeling, MLOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48c5c7e7de56c6fb</t>
+          <t>https://www.indeed.com/viewjob?jk=ff045a7655f5a9c1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Java)</t>
+          <t>Senior Specialist - Architecture</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Decatur, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Kafka, Data Modeling, MLOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338db949c564e874</t>
+          <t>https://www.indeed.com/viewjob?jk=38d9a99d3fb7e65b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Maximo Application Architect</t>
+          <t>Senior Analytics Engineer, Product</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>RAM Professional Services, LLC</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MongoDB, NoSQL, Power BI, Docker</t>
+          <t>RDS, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38110d7445c1f6a3</t>
+          <t>https://www.indeed.com/viewjob?jk=55bfb1f792ebb8b4</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Product Owner</t>
+          <t>Senior Analytics Engineer, Product</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Gallagher</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Rolling Meadows, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33815bde90512ef</t>
+          <t>https://www.indeed.com/viewjob?jk=c3759bc62b11d8fa</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Security Specialist Senior</t>
+          <t>Senior Analytics Engineer, Product</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7897b7e4bad68e</t>
+          <t>https://www.indeed.com/viewjob?jk=24e834cbb69e3e31</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Senior Data Engineer: $150-160,000, MN Based, Hybrid - 2 Days in Office</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>GovDocs</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, MongoDB, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb067c7ee9c6e671</t>
+          <t>https://www.indeed.com/viewjob?jk=8acefc49a07f2d39</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Senior Software Engineer ( Java)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Decatur, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4543a914df9789</t>
+          <t>https://www.indeed.com/viewjob?jk=338db949c564e874</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Power BI, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21cb7010e5a8a63</t>
+          <t>https://www.indeed.com/viewjob?jk=0855be7539fc7c3f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Angular / JAVA Full Stack Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, Azure, GCP, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6d4850de30c8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=fcfd60088aef43d3</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc22d977c810f0a5</t>
+          <t>https://www.indeed.com/viewjob?jk=eb067c7ee9c6e671</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Entry-level Moment Google Contact Center Developer</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26650088972ec91e</t>
+          <t>https://www.indeed.com/viewjob?jk=de4543a914df9789</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Trust &amp; Safety</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb78589d2a39e4df</t>
+          <t>https://www.indeed.com/viewjob?jk=f21cb7010e5a8a63</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Solution Engineer - Data Engineering Specialist - Bilingual (Spanish)</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a26823ec6dae45</t>
+          <t>https://www.indeed.com/viewjob?jk=5a6d4850de30c8ce</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Geospatial Solutions Architect</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,15 +3496,85 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc22d977c810f0a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Match Group</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kubernetes, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb78589d2a39e4df</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Geospatial Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>American business solutions inc</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5f71870dc0f7bc53</t>
         </is>

--- a/results/job_matches_2026-04-14.xlsx
+++ b/results/job_matches_2026-04-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Integration Engineer</t>
+          <t>Senior Data Engineer 2026 - US,UK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Parker's Kitchen</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,99 +696,99 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403fe46aec3ac312</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d01fdc4061dd2a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer 2026 - US,UK</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d01fdc4061dd2a</t>
+          <t>https://www.indeed.com/viewjob?jk=5f9a309f4efa98f8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Villanova University</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Villanova, PA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4acccdfc23951f0d</t>
+          <t>https://www.indeed.com/viewjob?jk=a513718316ea30dd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f9a309f4efa98f8</t>
+          <t>https://www.indeed.com/viewjob?jk=43cfe33e6a3659da</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Systems Operations Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C WATKINS &amp; ASSOCIATES</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f30f60cc3c36e72</t>
+          <t>https://www.indeed.com/viewjob?jk=620e166ed5473039</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a513718316ea30dd</t>
+          <t>https://www.indeed.com/viewjob?jk=ead7a3e6b1951593</t>
         </is>
       </c>
     </row>
@@ -893,20 +893,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43cfe33e6a3659da</t>
+          <t>https://www.indeed.com/viewjob?jk=f193a5a41b80d59d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620e166ed5473039</t>
+          <t>https://www.indeed.com/viewjob?jk=ae18e6a8860be459</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Software Engineer 3 - Contingent (contract)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ead7a3e6b1951593</t>
+          <t>https://www.indeed.com/viewjob?jk=7051fd3bf67a37ac</t>
         </is>
       </c>
     </row>
@@ -998,20 +998,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>The Cummings Agency</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f193a5a41b80d59d</t>
+          <t>https://www.indeed.com/viewjob?jk=91c4fcda77fa7425</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Mid-Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae18e6a8860be459</t>
+          <t>https://www.indeed.com/viewjob?jk=c717630a440c614c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Azure</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,59 +1091,59 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a406a8e4ff0f952d</t>
+          <t>https://www.indeed.com/viewjob?jk=15a32bf71ba33ffa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer 3 - Contingent (contract)</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7051fd3bf67a37ac</t>
+          <t>https://www.indeed.com/viewjob?jk=4d3db28285f41c46</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Cummings Agency</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91c4fcda77fa7425</t>
+          <t>https://www.indeed.com/viewjob?jk=3989068a8778fb79</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mid-Level Data Engineer, Global</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c717630a440c614c</t>
+          <t>https://www.indeed.com/viewjob?jk=5c70a1cb7dff6fb6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15a32bf71ba33ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=3de9b476cdbf12e9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Frida</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, IAM, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d3db28285f41c46</t>
+          <t>https://www.indeed.com/viewjob?jk=8900daeea8c64c35</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Software Development Engineer - Credential API</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,42 +1291,42 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3989068a8778fb79</t>
+          <t>https://www.indeed.com/viewjob?jk=88c29ef248c94981</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Data Support Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Illumen Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Stafford, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, Glue, Redshift, Athena, S3, Databricks, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c70a1cb7dff6fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=92cd661cf5a17182</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Engineer II – Big Data / ETL Engineer (Apptio)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>Databricks, BigQuery, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de9b476cdbf12e9</t>
+          <t>https://www.indeed.com/viewjob?jk=be9de9e1e7dbc172</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Reliability Engineer Oncology Analytics</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1388,15 +1388,15 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72b0fdeb9512d34e</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a8530ac9c848be</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Sys. Integration Sr. Specialist Advisor</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b78c747cdda3eb</t>
+          <t>https://www.indeed.com/viewjob?jk=43e632ec94c82b3b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Frida</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Star Schema</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,137 +1476,137 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8900daeea8c64c35</t>
+          <t>https://www.indeed.com/viewjob?jk=8a0467416d94bb26</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Credential API</t>
+          <t>Sr Mgr Data Engineering</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c29ef248c94981</t>
+          <t>https://www.indeed.com/viewjob?jk=03e707506ab6122a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Engineer II – Big Data / ETL Engineer (Apptio)</t>
+          <t>Intermediate Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>AWS, S3, Azure, Hadoop, Spark, Dask, Snowflake, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be9de9e1e7dbc172</t>
+          <t>https://www.indeed.com/viewjob?jk=2ccec05543d43588</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer Oncology Analytics</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a8530ac9c848be</t>
+          <t>https://www.indeed.com/viewjob?jk=bf17dcf23ea3201f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sys. Integration Sr. Specialist Advisor</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,102 +1616,102 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e632ec94c82b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=a1567499d777de5d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a0467416d94bb26</t>
+          <t>https://www.indeed.com/viewjob?jk=6177a38e86fbab44</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr Mgr Data Engineering</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e707506ab6122a</t>
+          <t>https://www.indeed.com/viewjob?jk=2722db66dd139366</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Aveva PI Software Engineer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Hive, Scala, DynamoDB, Splunk</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42dd34631f8a4a3a</t>
+          <t>https://www.indeed.com/viewjob?jk=ef58fd9ad5dd15ff</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>adonis</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Beacon, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81ac0513866a1f53</t>
+          <t>https://www.indeed.com/viewjob?jk=e5621c4e542d4639</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Intermediate Machine Learning Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Spark, Dask, Snowflake, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ccec05543d43588</t>
+          <t>https://www.indeed.com/viewjob?jk=38299c9de7d6d6a0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>NetApp Emerging Talent - Entry Level Software Engineer (Cloud Storage)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf17dcf23ea3201f</t>
+          <t>https://www.indeed.com/viewjob?jk=7e07865da969c4a3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Sr. Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Snowflake, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef58fd9ad5dd15ff</t>
+          <t>https://www.indeed.com/viewjob?jk=745ab30cde1846a7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6177a38e86fbab44</t>
+          <t>https://www.indeed.com/viewjob?jk=7a27a8acf3bc1bc8</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1567499d777de5d</t>
+          <t>https://www.indeed.com/viewjob?jk=ffb45764baeec647</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2722db66dd139366</t>
+          <t>https://www.indeed.com/viewjob?jk=02ca8eea8c20d4f1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>adonis</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5621c4e542d4639</t>
+          <t>https://www.indeed.com/viewjob?jk=93a9ff833b41ef5d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Pluto TV</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD, Git</t>
+          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38299c9de7d6d6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=46f1c7ebf3cba3e3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NetApp Emerging Talent - Entry Level Software Engineer (Cloud Storage)</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e07865da969c4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=fd62970232a35032</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Hybrid</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Snowflake, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=745ab30cde1846a7</t>
+          <t>https://www.indeed.com/viewjob?jk=e94dc1bfd30ae5f1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>NetApp Emerging Talent - Software Engineer (Cloud Storage)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a27a8acf3bc1bc8</t>
+          <t>https://www.indeed.com/viewjob?jk=4b72bdc255bbf6f8</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
+          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffb45764baeec647</t>
+          <t>https://www.indeed.com/viewjob?jk=f8bde7b210d67def</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ca8eea8c20d4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=dd96031899aef8e4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Databricks Lakehouse, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93a9ff833b41ef5d</t>
+          <t>https://www.indeed.com/viewjob?jk=a6e81f16ad428334</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>2026009 - Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>John Deere</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Moline, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,112 +2271,112 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Scala, PostgreSQL, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f1c7ebf3cba3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=45e1a444de87fc2c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>RNGD</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd62970232a35032</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a3ecae4bdb7e4b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>MachineMetrics, Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, RDS, Scala, Kafka, PostgreSQL, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e94dc1bfd30ae5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=80173e5fca484063</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Dynatrace Observability Engineer</t>
+          <t>Microsoft Modern Work Consultant</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Core BTS</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=504c2eb153af2545</t>
+          <t>https://www.indeed.com/viewjob?jk=11d034c0b8905492</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Infrastructure, Architect</t>
+          <t>Senior DevOps Cloud Engineer (Information Technology Subject Matter Expert)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Western Union</t>
+          <t>State of Connecticut</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Oracle, Cassandra, Splunk, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=719c318bdfe0b93a</t>
+          <t>https://www.indeed.com/viewjob?jk=d267e859d5950f5a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test</t>
+          <t>Data Tester (Python) - 6254091</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Databricks Lakehouse, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, PySpark, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6e81f16ad428334</t>
+          <t>https://www.indeed.com/viewjob?jk=89141221ea154795</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Developer</t>
+          <t>Senior Geospatial Solutions Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>S R International Inc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Kubernetes, Python</t>
+          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc89b8593855079</t>
+          <t>https://www.indeed.com/viewjob?jk=b4968b1c75b8ea91</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NetApp Emerging Talent - Software Engineer (Cloud Storage)</t>
+          <t>Senior Geospatial Solutions Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,102 +2526,102 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b72bdc255bbf6f8</t>
+          <t>https://www.indeed.com/viewjob?jk=5f71870dc0f7bc53</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
+          <t>Angular / JAVA Full Stack Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8bde7b210d67def</t>
+          <t>https://www.indeed.com/viewjob?jk=fcfd60088aef43d3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
+          <t>Senior Data Engineer: $150-160,000, MN Based, Hybrid - 2 Days in Office</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>GovDocs</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, MongoDB, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd96031899aef8e4</t>
+          <t>https://www.indeed.com/viewjob?jk=8acefc49a07f2d39</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026009 - Software Engineer</t>
+          <t>Senior Software Engineer (AI Enablement)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>John Deere</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Moline, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Scala, PostgreSQL, Docker, Kubernetes, SonarQube</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e1a444de87fc2c</t>
+          <t>https://www.indeed.com/viewjob?jk=48c5c7e7de56c6fb</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer ( Java)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MachineMetrics, Inc.</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Decatur, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, RDS, Scala, Kafka, PostgreSQL, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80173e5fca484063</t>
+          <t>https://www.indeed.com/viewjob?jk=338db949c564e874</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Microsoft Modern Work Consultant</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d034c0b8905492</t>
+          <t>https://www.indeed.com/viewjob?jk=eb067c7ee9c6e671</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer (Information Technology Subject Matter Expert)</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>State of Connecticut</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d267e859d5950f5a</t>
+          <t>https://www.indeed.com/viewjob?jk=de4543a914df9789</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Tester (Python) - 6254091</t>
+          <t>Senior Analytics Engineer, Product</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, PySpark, ETL, ELT, CI/CD</t>
+          <t>RDS, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89141221ea154795</t>
+          <t>https://www.indeed.com/viewjob?jk=55bfb1f792ebb8b4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Analytics Engineer, Product</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Path Robotics, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
+          <t>RDS, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0c06f03d80ad17</t>
+          <t>https://www.indeed.com/viewjob?jk=c3759bc62b11d8fa</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Maximo Application Architect</t>
+          <t>Senior Analytics Engineer, Product</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>RAM Professional Services, LLC</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MongoDB, NoSQL, Power BI, Docker</t>
+          <t>RDS, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38110d7445c1f6a3</t>
+          <t>https://www.indeed.com/viewjob?jk=24e834cbb69e3e31</t>
         </is>
       </c>
     </row>
@@ -2883,17 +2883,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Geospatial Solutions Architect</t>
+          <t>Senior Machine Learning Engineer, Trust &amp; Safety</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>S R International Inc</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,682 +2901,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4968b1c75b8ea91</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (AI Enablement)</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Redwood Logistics</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48c5c7e7de56c6fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Security Specialist Senior</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>PNC Financial Services Group</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Azure, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7897b7e4bad68e</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Senior Specialist - Architecture</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>LTIMindtree</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Kafka, Data Modeling, MLOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=18e84b525a6d6412</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Senior Specialist - Architecture</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>LTIMindtree</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Berkeley Heights, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Kafka, Data Modeling, MLOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff045a7655f5a9c1</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Senior Specialist - Architecture</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>LTIMindtree</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Kafka, Data Modeling, MLOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=38d9a99d3fb7e65b</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer, Product</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=55bfb1f792ebb8b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer, Product</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c3759bc62b11d8fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer, Product</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24e834cbb69e3e31</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer: $150-160,000, MN Based, Hybrid - 2 Days in Office</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>GovDocs</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Saint Paul, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, MongoDB, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8acefc49a07f2d39</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer ( Java)</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Press Ganey</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Decatur, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=338db949c564e874</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Senior Python Developer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Bentonville, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Power BI, Airflow</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0855be7539fc7c3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Angular / JAVA Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Charles Schwab</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fcfd60088aef43d3</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Salesforce Data Cloud Architect</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>EPAM Systems</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb067c7ee9c6e671</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Salesforce Data Cloud Architect</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>EPAM Systems</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=de4543a914df9789</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f21cb7010e5a8a63</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6d4850de30c8ce</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dc22d977c810f0a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer, Trust &amp; Safety</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Match Group</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kubernetes, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=fb78589d2a39e4df</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Senior Geospatial Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>American business solutions inc</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5f71870dc0f7bc53</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-14.xlsx
+++ b/results/job_matches_2026-04-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,12 +853,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Architect I</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -867,38 +867,38 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ead7a3e6b1951593</t>
+          <t>https://www.indeed.com/viewjob?jk=c6d97da40a8da560</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,19 +916,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f193a5a41b80d59d</t>
+          <t>https://www.indeed.com/viewjob?jk=ead7a3e6b1951593</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae18e6a8860be459</t>
+          <t>https://www.indeed.com/viewjob?jk=f193a5a41b80d59d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer 3 - Contingent (contract)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,69 +976,69 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7051fd3bf67a37ac</t>
+          <t>https://www.indeed.com/viewjob?jk=ae18e6a8860be459</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer 3 - Contingent (contract)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Cummings Agency</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91c4fcda77fa7425</t>
+          <t>https://www.indeed.com/viewjob?jk=7051fd3bf67a37ac</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mid-Level Data Engineer, Global</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c717630a440c614c</t>
+          <t>https://www.indeed.com/viewjob?jk=072e6e4e8e025141</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Mid-Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15a32bf71ba33ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=c717630a440c614c</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d3db28285f41c46</t>
+          <t>https://www.indeed.com/viewjob?jk=15a32bf71ba33ffa</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3989068a8778fb79</t>
+          <t>https://www.indeed.com/viewjob?jk=4d3db28285f41c46</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c70a1cb7dff6fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=3989068a8778fb79</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de9b476cdbf12e9</t>
+          <t>https://www.indeed.com/viewjob?jk=5c70a1cb7dff6fb6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Frida</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Star Schema</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8900daeea8c64c35</t>
+          <t>https://www.indeed.com/viewjob?jk=3de9b476cdbf12e9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Credential API</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Frida</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,69 +1291,69 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, IAM, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c29ef248c94981</t>
+          <t>https://www.indeed.com/viewjob?jk=8900daeea8c64c35</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Support Engineer</t>
+          <t>Software Development Engineer - Credential API</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Illumen Group</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Stafford, VA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, Databricks, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92cd661cf5a17182</t>
+          <t>https://www.indeed.com/viewjob?jk=88c29ef248c94981</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Engineer II – Big Data / ETL Engineer (Apptio)</t>
+          <t>Data Support Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Illumen Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Stafford, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Redshift, Athena, S3, Databricks, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be9de9e1e7dbc172</t>
+          <t>https://www.indeed.com/viewjob?jk=92cd661cf5a17182</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer Oncology Analytics</t>
+          <t>Engineer II – Big Data / ETL Engineer (Apptio)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>Databricks, BigQuery, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a8530ac9c848be</t>
+          <t>https://www.indeed.com/viewjob?jk=be9de9e1e7dbc172</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sys. Integration Sr. Specialist Advisor</t>
+          <t>Data Reliability Engineer Oncology Analytics</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e632ec94c82b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a8530ac9c848be</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Intermediate Machine Learning Data Engineer</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Spark, Dask, Snowflake, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ccec05543d43588</t>
+          <t>https://www.indeed.com/viewjob?jk=62c75d5f8fbde70d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Medeloop</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,19 +1581,19 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf17dcf23ea3201f</t>
+          <t>https://www.indeed.com/viewjob?jk=a81ed0b08e8f07f7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Intermediate Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, S3, Azure, Hadoop, Spark, Dask, Snowflake, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1567499d777de5d</t>
+          <t>https://www.indeed.com/viewjob?jk=2ccec05543d43588</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2722db66dd139366</t>
+          <t>https://www.indeed.com/viewjob?jk=a1567499d777de5d</t>
         </is>
       </c>
     </row>
@@ -1728,60 +1728,60 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>adonis</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5621c4e542d4639</t>
+          <t>https://www.indeed.com/viewjob?jk=2722db66dd139366</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD, Git</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38299c9de7d6d6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=bf17dcf23ea3201f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NetApp Emerging Talent - Entry Level Software Engineer (Cloud Storage)</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>adonis</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e07865da969c4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=e5621c4e542d4639</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Hybrid</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Snowflake, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=745ab30cde1846a7</t>
+          <t>https://www.indeed.com/viewjob?jk=38299c9de7d6d6a0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>NetApp Emerging Talent - Entry Level Software Engineer (Cloud Storage)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a27a8acf3bc1bc8</t>
+          <t>https://www.indeed.com/viewjob?jk=7e07865da969c4a3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
+          <t>Sr. Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Snowflake, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffb45764baeec647</t>
+          <t>https://www.indeed.com/viewjob?jk=745ab30cde1846a7</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1961,29 +1961,29 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ca8eea8c20d4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=7a27a8acf3bc1bc8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93a9ff833b41ef5d</t>
+          <t>https://www.indeed.com/viewjob?jk=ffb45764baeec647</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f1c7ebf3cba3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=02ca8eea8c20d4f1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd62970232a35032</t>
+          <t>https://www.indeed.com/viewjob?jk=93a9ff833b41ef5d</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e94dc1bfd30ae5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=fd62970232a35032</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NetApp Emerging Talent - Software Engineer (Cloud Storage)</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b72bdc255bbf6f8</t>
+          <t>https://www.indeed.com/viewjob?jk=e94dc1bfd30ae5f1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
+          <t>Full-Stack Developer (AWS, TS, React)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8bde7b210d67def</t>
+          <t>https://www.indeed.com/viewjob?jk=cc3a148287061e68</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Rocket Close</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd96031899aef8e4</t>
+          <t>https://www.indeed.com/viewjob?jk=9fce91f5c39bd4ed</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test</t>
+          <t>NetApp Emerging Talent - Software Engineer (Cloud Storage)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Databricks Lakehouse, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6e81f16ad428334</t>
+          <t>https://www.indeed.com/viewjob?jk=4b72bdc255bbf6f8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026009 - Software Engineer</t>
+          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>John Deere</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Moline, IL, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,64 +2271,64 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Scala, PostgreSQL, Docker, Kubernetes, SonarQube</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e1a444de87fc2c</t>
+          <t>https://www.indeed.com/viewjob?jk=f8bde7b210d67def</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II (HYBRID MA OR REMOTE)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RNGD</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a3ecae4bdb7e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=dd96031899aef8e4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MachineMetrics, Inc.</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2337,11 +2337,11 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, RDS, Scala, Kafka, PostgreSQL, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Databricks Lakehouse, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80173e5fca484063</t>
+          <t>https://www.indeed.com/viewjob?jk=a6e81f16ad428334</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Microsoft Modern Work Consultant</t>
+          <t>2026009 - Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>John Deere</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Moline, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Scala, PostgreSQL, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d034c0b8905492</t>
+          <t>https://www.indeed.com/viewjob?jk=45e1a444de87fc2c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer (Information Technology Subject Matter Expert)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>State of Connecticut</t>
+          <t>RNGD</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d267e859d5950f5a</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a3ecae4bdb7e4b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Tester (Python) - 6254091</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>MachineMetrics, Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, PySpark, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, RDS, Scala, Kafka, PostgreSQL, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89141221ea154795</t>
+          <t>https://www.indeed.com/viewjob?jk=80173e5fca484063</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Geospatial Solutions Architect</t>
+          <t>Microsoft Modern Work Consultant</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>S R International Inc</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4968b1c75b8ea91</t>
+          <t>https://www.indeed.com/viewjob?jk=11d034c0b8905492</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Geospatial Solutions Architect</t>
+          <t>Senior DevOps Cloud Engineer (Information Technology Subject Matter Expert)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>State of Connecticut</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f71870dc0f7bc53</t>
+          <t>https://www.indeed.com/viewjob?jk=d267e859d5950f5a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Angular / JAVA Full Stack Engineer</t>
+          <t>Software Developer - Information Governance</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcfd60088aef43d3</t>
+          <t>https://www.indeed.com/viewjob?jk=65cd9651c7e25101</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer: $150-160,000, MN Based, Hybrid - 2 Days in Office</t>
+          <t>Data Tester (Python) - 6254091</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GovDocs</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, MongoDB, ETL, ELT, Power BI, CI/CD</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, PySpark, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8acefc49a07f2d39</t>
+          <t>https://www.indeed.com/viewjob?jk=89141221ea154795</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AI Enablement)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48c5c7e7de56c6fb</t>
+          <t>https://www.indeed.com/viewjob?jk=085872f73883326c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Java)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Decatur, GA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338db949c564e874</t>
+          <t>https://www.indeed.com/viewjob?jk=fa79af047e73dc3e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb067c7ee9c6e671</t>
+          <t>https://www.indeed.com/viewjob?jk=34987f860a590c53</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Angular / JAVA Full Stack Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, S3, Azure, GCP, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4543a914df9789</t>
+          <t>https://www.indeed.com/viewjob?jk=fcfd60088aef43d3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Product</t>
+          <t>Senior Data Engineer: $150-160,000, MN Based, Hybrid - 2 Days in Office</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>GovDocs</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, MongoDB, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55bfb1f792ebb8b4</t>
+          <t>https://www.indeed.com/viewjob?jk=8acefc49a07f2d39</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Product</t>
+          <t>Senior Software Engineer (AI Enablement)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3759bc62b11d8fa</t>
+          <t>https://www.indeed.com/viewjob?jk=48c5c7e7de56c6fb</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Product</t>
+          <t>Senior Software Engineer ( Java)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Decatur, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e834cbb69e3e31</t>
+          <t>https://www.indeed.com/viewjob?jk=338db949c564e874</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Product Owner</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Gallagher</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Rolling Meadows, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33815bde90512ef</t>
+          <t>https://www.indeed.com/viewjob?jk=eb067c7ee9c6e671</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Trust &amp; Safety</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,17 +2901,262 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de4543a914df9789</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Match Group</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kubernetes, Airflow, Git</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>2026-04-13</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fb78589d2a39e4df</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer, Product</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55bfb1f792ebb8b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer, Product</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3759bc62b11d8fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer, Product</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24e834cbb69e3e31</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Data Product Owner</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Gallagher</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Rolling Meadows, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a33815bde90512ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Geospatial Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>S R International Inc</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4968b1c75b8ea91</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior Geospatial Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>American business solutions inc</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f71870dc0f7bc53</t>
         </is>
       </c>
     </row>
